--- a/Oferta CRV.xlsx
+++ b/Oferta CRV.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anna/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anna/Desktop/KalkulatorInbredu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{057BAA87-CF53-B04C-BCFA-DAAC8C790F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6FA2CA-AD31-1F44-8729-D4F03054C168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="5760" windowWidth="28800" windowHeight="16180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="640" windowWidth="28800" windowHeight="16180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="563">
   <si>
     <t>Stada</t>
   </si>
@@ -1635,6 +1635,93 @@
   </si>
   <si>
     <t xml:space="preserve">RUSH HOUR CD   </t>
+  </si>
+  <si>
+    <t>ID_Maternal_Grand_Dam_Sire</t>
+  </si>
+  <si>
+    <t>NLDM000718437783</t>
+  </si>
+  <si>
+    <t>NLDM000687206379</t>
+  </si>
+  <si>
+    <t>NLDM000765206109</t>
+  </si>
+  <si>
+    <t>USAM000143189741</t>
+  </si>
+  <si>
+    <t>NLDM000921967114</t>
+  </si>
+  <si>
+    <t>NLDM000738287780</t>
+  </si>
+  <si>
+    <t>DNKM000000258449</t>
+  </si>
+  <si>
+    <t>FRAM007297006288</t>
+  </si>
+  <si>
+    <t>DEUM000667337098</t>
+  </si>
+  <si>
+    <t>NLDM000666841779</t>
+  </si>
+  <si>
+    <t>NLDM000665667174</t>
+  </si>
+  <si>
+    <t>NLDM000671732952</t>
+  </si>
+  <si>
+    <t>NLDM000633377638</t>
+  </si>
+  <si>
+    <t>DEUM000770248602</t>
+  </si>
+  <si>
+    <t>BELM000313114634</t>
+  </si>
+  <si>
+    <t>USAM000072128125</t>
+  </si>
+  <si>
+    <t>DEUM000356607584</t>
+  </si>
+  <si>
+    <t>NLDM000767212247</t>
+  </si>
+  <si>
+    <t>NLDM000755898903</t>
+  </si>
+  <si>
+    <t>NLDM000754716712</t>
+  </si>
+  <si>
+    <t>USAM000072156794</t>
+  </si>
+  <si>
+    <t>NLDM000573352412</t>
+  </si>
+  <si>
+    <t>USAM003140986372</t>
+  </si>
+  <si>
+    <t>NLDM000922014358</t>
+  </si>
+  <si>
+    <t>NLDM000663103102</t>
+  </si>
+  <si>
+    <t>USAM000072128216</t>
+  </si>
+  <si>
+    <t>USAM003128557482</t>
+  </si>
+  <si>
+    <t>USAM003134652431</t>
   </si>
 </sst>
 </file>
@@ -1644,7 +1731,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1703,6 +1790,18 @@
       <family val="2"/>
       <charset val="238"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1755,7 +1854,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1788,6 +1887,9 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -2071,43 +2173,45 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AQ52"/>
+  <dimension ref="A1:AR52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1640625" style="1" customWidth="1"/>
-    <col min="14" max="15" width="12.1640625" customWidth="1"/>
-    <col min="16" max="16" width="7.5" customWidth="1"/>
-    <col min="17" max="17" width="5" customWidth="1"/>
-    <col min="18" max="18" width="4.83203125" customWidth="1"/>
-    <col min="19" max="19" width="8" customWidth="1"/>
-    <col min="20" max="20" width="8.83203125" customWidth="1"/>
-    <col min="21" max="21" width="9.5" customWidth="1"/>
-    <col min="22" max="22" width="7.33203125" customWidth="1"/>
-    <col min="23" max="23" width="8" customWidth="1"/>
-    <col min="24" max="24" width="4.5" customWidth="1"/>
-    <col min="25" max="25" width="6.33203125" customWidth="1"/>
-    <col min="26" max="26" width="11" customWidth="1"/>
-    <col min="27" max="27" width="4.1640625" customWidth="1"/>
-    <col min="28" max="28" width="4.33203125" customWidth="1"/>
-    <col min="29" max="29" width="10.33203125" customWidth="1"/>
-    <col min="30" max="30" width="16.5" customWidth="1"/>
-    <col min="31" max="31" width="7.5" customWidth="1"/>
-    <col min="32" max="32" width="4.33203125" customWidth="1"/>
-    <col min="33" max="33" width="5" customWidth="1"/>
-    <col min="34" max="34" width="13.1640625" customWidth="1"/>
-    <col min="35" max="35" width="16.6640625" customWidth="1"/>
-    <col min="36" max="36" width="4.5" customWidth="1"/>
-    <col min="37" max="37" width="14" customWidth="1"/>
-    <col min="38" max="38" width="14.6640625" customWidth="1"/>
-    <col min="39" max="39" width="6" customWidth="1"/>
-    <col min="40" max="40" width="14.33203125" customWidth="1"/>
-    <col min="41" max="41" width="9.6640625" customWidth="1"/>
-    <col min="42" max="42" width="14.33203125" customWidth="1"/>
-    <col min="43" max="43" width="17.33203125" customWidth="1"/>
+    <col min="9" max="9" width="18.5" customWidth="1"/>
+    <col min="12" max="12" width="19.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.1640625" style="1" customWidth="1"/>
+    <col min="15" max="16" width="12.1640625" customWidth="1"/>
+    <col min="17" max="17" width="7.5" customWidth="1"/>
+    <col min="18" max="18" width="5" customWidth="1"/>
+    <col min="19" max="19" width="4.83203125" customWidth="1"/>
+    <col min="20" max="20" width="8" customWidth="1"/>
+    <col min="21" max="21" width="8.83203125" customWidth="1"/>
+    <col min="22" max="22" width="9.5" customWidth="1"/>
+    <col min="23" max="23" width="7.33203125" customWidth="1"/>
+    <col min="24" max="24" width="8" customWidth="1"/>
+    <col min="25" max="25" width="4.5" customWidth="1"/>
+    <col min="26" max="26" width="6.33203125" customWidth="1"/>
+    <col min="27" max="27" width="11" customWidth="1"/>
+    <col min="28" max="28" width="4.1640625" customWidth="1"/>
+    <col min="29" max="29" width="4.33203125" customWidth="1"/>
+    <col min="30" max="30" width="10.33203125" customWidth="1"/>
+    <col min="31" max="31" width="16.5" customWidth="1"/>
+    <col min="32" max="32" width="7.5" customWidth="1"/>
+    <col min="33" max="33" width="4.33203125" customWidth="1"/>
+    <col min="34" max="34" width="5" customWidth="1"/>
+    <col min="35" max="35" width="13.1640625" customWidth="1"/>
+    <col min="36" max="36" width="16.6640625" customWidth="1"/>
+    <col min="37" max="37" width="4.5" customWidth="1"/>
+    <col min="38" max="38" width="14" customWidth="1"/>
+    <col min="39" max="39" width="14.6640625" customWidth="1"/>
+    <col min="40" max="40" width="6" customWidth="1"/>
+    <col min="41" max="41" width="14.33203125" customWidth="1"/>
+    <col min="42" max="42" width="9.6640625" customWidth="1"/>
+    <col min="43" max="43" width="14.33203125" customWidth="1"/>
+    <col min="44" max="44" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>112</v>
       </c>
@@ -2141,104 +2245,107 @@
       <c r="K1" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="15" t="s">
+        <v>534</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>390</v>
       </c>
@@ -2272,102 +2379,105 @@
       <c r="K2" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="M2" s="2">
         <v>44069</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="N2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P2" s="9">
+      <c r="Q2" s="9">
         <v>91</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="R2" s="9">
         <v>717</v>
       </c>
-      <c r="R2" s="9">
+      <c r="S2" s="9">
         <v>325</v>
       </c>
-      <c r="S2" s="9">
+      <c r="T2" s="9">
         <v>1026</v>
       </c>
-      <c r="T2" s="10">
+      <c r="U2" s="10">
         <v>-0.23</v>
       </c>
-      <c r="U2" s="9">
+      <c r="V2" s="9">
         <v>20</v>
       </c>
-      <c r="V2" s="10">
+      <c r="W2" s="10">
         <v>0.05</v>
       </c>
-      <c r="W2" s="9">
+      <c r="X2" s="9">
         <v>42</v>
       </c>
-      <c r="X2" s="9">
+      <c r="Y2" s="9">
         <v>105</v>
       </c>
-      <c r="Y2" s="9">
+      <c r="Z2" s="9">
         <v>106</v>
       </c>
-      <c r="Z2" s="9">
+      <c r="AA2" s="9">
         <v>105</v>
       </c>
-      <c r="AA2" s="9">
+      <c r="AB2" s="9">
         <v>179</v>
       </c>
-      <c r="AB2" s="9">
+      <c r="AC2" s="9">
         <v>107</v>
       </c>
-      <c r="AC2" s="9">
+      <c r="AD2" s="9">
         <v>102</v>
       </c>
-      <c r="AD2" s="9">
+      <c r="AE2" s="9">
         <v>100</v>
       </c>
-      <c r="AE2" s="9"/>
-      <c r="AF2" s="9">
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="9">
         <v>12</v>
       </c>
-      <c r="AG2" s="9">
+      <c r="AH2" s="9">
         <v>241</v>
       </c>
-      <c r="AH2" s="9">
+      <c r="AI2" s="9">
         <v>349</v>
       </c>
-      <c r="AI2" s="9">
+      <c r="AJ2" s="9">
         <v>106</v>
       </c>
-      <c r="AJ2" s="9">
+      <c r="AK2" s="9">
         <v>4</v>
       </c>
-      <c r="AK2" s="9">
+      <c r="AL2" s="9">
         <v>105</v>
       </c>
-      <c r="AL2" s="9">
+      <c r="AM2" s="9">
         <v>108</v>
       </c>
-      <c r="AM2" s="9">
+      <c r="AN2" s="9">
         <v>101</v>
       </c>
-      <c r="AN2" s="9">
+      <c r="AO2" s="9">
         <v>104</v>
       </c>
-      <c r="AO2" s="9">
+      <c r="AP2" s="9">
         <v>98</v>
       </c>
-      <c r="AP2" s="9">
+      <c r="AQ2" s="9">
         <v>103</v>
       </c>
-      <c r="AQ2" s="9">
+      <c r="AR2" s="9">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>101</v>
       </c>
@@ -2401,102 +2511,105 @@
       <c r="K3" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M3" s="2">
         <v>43987</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="N3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P3" s="9">
+      <c r="Q3" s="9">
         <v>93</v>
       </c>
-      <c r="Q3" s="9">
+      <c r="R3" s="9">
         <v>4558</v>
       </c>
-      <c r="R3" s="9">
+      <c r="S3" s="9">
         <v>1295</v>
       </c>
-      <c r="S3" s="9">
+      <c r="T3" s="9">
         <v>587</v>
       </c>
-      <c r="T3" s="10">
+      <c r="U3" s="10">
         <v>0.33</v>
       </c>
-      <c r="U3" s="9">
+      <c r="V3" s="9">
         <v>59</v>
       </c>
-      <c r="V3" s="10">
+      <c r="W3" s="10">
         <v>0.25</v>
       </c>
-      <c r="W3" s="9">
+      <c r="X3" s="9">
         <v>46</v>
       </c>
-      <c r="X3" s="9">
+      <c r="Y3" s="9">
         <v>110</v>
       </c>
-      <c r="Y3" s="9">
+      <c r="Z3" s="9">
         <v>104</v>
       </c>
-      <c r="Z3" s="9">
+      <c r="AA3" s="9">
         <v>109</v>
       </c>
-      <c r="AA3" s="9">
+      <c r="AB3" s="9">
         <v>252</v>
       </c>
-      <c r="AB3" s="9">
+      <c r="AC3" s="9">
         <v>105</v>
       </c>
-      <c r="AC3" s="9">
+      <c r="AD3" s="9">
         <v>96</v>
       </c>
-      <c r="AD3" s="9">
+      <c r="AE3" s="9">
         <v>105</v>
       </c>
-      <c r="AE3" s="9"/>
-      <c r="AF3" s="9">
+      <c r="AF3" s="9"/>
+      <c r="AG3" s="9">
         <v>10</v>
       </c>
-      <c r="AG3" s="9">
+      <c r="AH3" s="9">
         <v>375</v>
       </c>
-      <c r="AH3" s="9">
+      <c r="AI3" s="9">
         <v>401</v>
       </c>
-      <c r="AI3" s="9">
+      <c r="AJ3" s="9">
         <v>106</v>
       </c>
-      <c r="AJ3" s="9">
+      <c r="AK3" s="9">
         <v>5</v>
       </c>
-      <c r="AK3" s="9">
+      <c r="AL3" s="9">
         <v>105</v>
       </c>
-      <c r="AL3" s="9">
+      <c r="AM3" s="9">
         <v>110</v>
       </c>
-      <c r="AM3" s="9">
+      <c r="AN3" s="9">
         <v>105</v>
       </c>
-      <c r="AN3" s="9">
+      <c r="AO3" s="9">
         <v>100</v>
-      </c>
-      <c r="AO3" s="9">
-        <v>99</v>
       </c>
       <c r="AP3" s="9">
         <v>99</v>
       </c>
       <c r="AQ3" s="9">
+        <v>99</v>
+      </c>
+      <c r="AR3" s="9">
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>131</v>
       </c>
@@ -2530,102 +2643,105 @@
       <c r="K4" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="M4" s="2">
         <v>45028</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="P4" s="9">
+      <c r="Q4" s="9">
         <v>78</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>0</v>
       </c>
       <c r="R4" s="9">
         <v>0</v>
       </c>
       <c r="S4" s="9">
+        <v>0</v>
+      </c>
+      <c r="T4" s="9">
         <v>1824</v>
       </c>
-      <c r="T4" s="10">
+      <c r="U4" s="10">
         <v>-0.22</v>
       </c>
-      <c r="U4" s="9">
+      <c r="V4" s="9">
         <v>53</v>
       </c>
-      <c r="V4" s="10">
+      <c r="W4" s="10">
         <v>-0.02</v>
       </c>
-      <c r="W4" s="9">
+      <c r="X4" s="9">
         <v>62</v>
       </c>
-      <c r="X4" s="9">
+      <c r="Y4" s="9">
         <v>101</v>
       </c>
-      <c r="Y4" s="9">
+      <c r="Z4" s="9">
         <v>110</v>
       </c>
-      <c r="Z4" s="9">
+      <c r="AA4" s="9">
         <v>107</v>
       </c>
-      <c r="AA4" s="9">
+      <c r="AB4" s="9">
         <v>291</v>
       </c>
-      <c r="AB4" s="9">
+      <c r="AC4" s="9">
         <v>106</v>
-      </c>
-      <c r="AC4" s="9">
-        <v>100</v>
       </c>
       <c r="AD4" s="9">
         <v>100</v>
       </c>
-      <c r="AE4" s="9"/>
-      <c r="AF4" s="9">
+      <c r="AE4" s="9">
+        <v>100</v>
+      </c>
+      <c r="AF4" s="9"/>
+      <c r="AG4" s="9">
         <v>12</v>
       </c>
-      <c r="AG4" s="9">
+      <c r="AH4" s="9">
         <v>426</v>
       </c>
-      <c r="AH4" s="9">
+      <c r="AI4" s="9">
         <v>446</v>
       </c>
-      <c r="AI4" s="9">
+      <c r="AJ4" s="9">
         <v>106</v>
       </c>
-      <c r="AJ4" s="9">
+      <c r="AK4" s="9">
         <v>6</v>
       </c>
-      <c r="AK4" s="9">
+      <c r="AL4" s="9">
         <v>105</v>
       </c>
-      <c r="AL4" s="9">
+      <c r="AM4" s="9">
         <v>107</v>
       </c>
-      <c r="AM4" s="9">
+      <c r="AN4" s="9">
         <v>102</v>
       </c>
-      <c r="AN4" s="9">
+      <c r="AO4" s="9">
         <v>106</v>
       </c>
-      <c r="AO4" s="9">
+      <c r="AP4" s="9">
         <v>107</v>
       </c>
-      <c r="AP4" s="9">
+      <c r="AQ4" s="9">
         <v>100</v>
       </c>
-      <c r="AQ4" s="9">
+      <c r="AR4" s="9">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>104</v>
       </c>
@@ -2659,104 +2775,107 @@
       <c r="K5" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="M5" s="2">
         <v>43308</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="N5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P5" s="9">
+      <c r="Q5" s="9">
         <v>99</v>
       </c>
-      <c r="Q5" s="9">
+      <c r="R5" s="9">
         <v>7523</v>
       </c>
-      <c r="R5" s="9">
+      <c r="S5" s="9">
         <v>1707</v>
       </c>
-      <c r="S5" s="9">
+      <c r="T5" s="9">
         <v>2185</v>
       </c>
-      <c r="T5" s="10">
+      <c r="U5" s="10">
         <v>-0.08</v>
       </c>
-      <c r="U5" s="9">
+      <c r="V5" s="9">
         <v>85</v>
       </c>
-      <c r="V5" s="10">
+      <c r="W5" s="10">
         <v>-0.01</v>
       </c>
-      <c r="W5" s="9">
+      <c r="X5" s="9">
         <v>76</v>
       </c>
-      <c r="X5" s="9">
+      <c r="Y5" s="9">
         <v>106</v>
       </c>
-      <c r="Y5" s="9">
+      <c r="Z5" s="9">
         <v>108</v>
       </c>
-      <c r="Z5" s="9">
+      <c r="AA5" s="9">
         <v>109</v>
       </c>
-      <c r="AA5" s="9">
+      <c r="AB5" s="9">
         <v>276</v>
       </c>
-      <c r="AB5" s="9">
+      <c r="AC5" s="9">
         <v>108</v>
       </c>
-      <c r="AC5" s="9">
+      <c r="AD5" s="9">
         <v>97</v>
       </c>
-      <c r="AD5" s="9">
+      <c r="AE5" s="9">
         <v>94</v>
       </c>
-      <c r="AE5" s="9">
+      <c r="AF5" s="9">
         <v>89</v>
       </c>
-      <c r="AF5" s="9">
+      <c r="AG5" s="9">
         <v>18</v>
       </c>
-      <c r="AG5" s="9">
+      <c r="AH5" s="9">
         <v>582</v>
       </c>
-      <c r="AH5" s="9">
+      <c r="AI5" s="9">
         <v>409</v>
       </c>
-      <c r="AI5" s="9">
+      <c r="AJ5" s="9">
         <v>112</v>
       </c>
-      <c r="AJ5" s="9">
+      <c r="AK5" s="9">
         <v>1</v>
-      </c>
-      <c r="AK5" s="9">
-        <v>106</v>
       </c>
       <c r="AL5" s="9">
         <v>106</v>
       </c>
       <c r="AM5" s="9">
+        <v>106</v>
+      </c>
+      <c r="AN5" s="9">
         <v>97</v>
       </c>
-      <c r="AN5" s="9">
+      <c r="AO5" s="9">
         <v>100</v>
       </c>
-      <c r="AO5" s="9">
+      <c r="AP5" s="9">
         <v>92</v>
       </c>
-      <c r="AP5" s="9">
+      <c r="AQ5" s="9">
         <v>101</v>
       </c>
-      <c r="AQ5" s="9">
+      <c r="AR5" s="9">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>398</v>
       </c>
@@ -2790,102 +2909,105 @@
       <c r="K6" s="12" t="s">
         <v>408</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="M6" s="2">
         <v>44837</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="N6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="P6" s="9">
+      <c r="Q6" s="9">
         <v>79</v>
-      </c>
-      <c r="Q6" s="9">
-        <v>0</v>
       </c>
       <c r="R6" s="9">
         <v>0</v>
       </c>
       <c r="S6" s="9">
+        <v>0</v>
+      </c>
+      <c r="T6" s="9">
         <v>1705</v>
       </c>
-      <c r="T6" s="10">
+      <c r="U6" s="10">
         <v>-0.28999999999999998</v>
       </c>
-      <c r="U6" s="9">
+      <c r="V6" s="9">
         <v>41</v>
       </c>
-      <c r="V6" s="10">
+      <c r="W6" s="10">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="W6" s="9">
+      <c r="X6" s="9">
         <v>44</v>
       </c>
-      <c r="X6" s="9">
+      <c r="Y6" s="9">
         <v>104</v>
       </c>
-      <c r="Y6" s="9">
+      <c r="Z6" s="9">
         <v>102</v>
       </c>
-      <c r="Z6" s="9">
+      <c r="AA6" s="9">
         <v>105</v>
       </c>
-      <c r="AA6" s="9">
+      <c r="AB6" s="9">
         <v>189</v>
       </c>
-      <c r="AB6" s="9">
+      <c r="AC6" s="9">
         <v>106</v>
       </c>
-      <c r="AC6" s="9">
+      <c r="AD6" s="9">
         <v>93</v>
       </c>
-      <c r="AD6" s="9">
+      <c r="AE6" s="9">
         <v>97</v>
       </c>
-      <c r="AE6" s="9"/>
-      <c r="AF6" s="9">
+      <c r="AF6" s="9"/>
+      <c r="AG6" s="9">
         <v>10</v>
       </c>
-      <c r="AG6" s="9">
+      <c r="AH6" s="9">
         <v>312</v>
       </c>
-      <c r="AH6" s="9">
+      <c r="AI6" s="9">
         <v>525</v>
       </c>
-      <c r="AI6" s="9">
+      <c r="AJ6" s="9">
         <v>105</v>
       </c>
-      <c r="AJ6" s="9">
+      <c r="AK6" s="9">
         <v>2</v>
       </c>
-      <c r="AK6" s="9">
+      <c r="AL6" s="9">
         <v>106</v>
       </c>
-      <c r="AL6" s="9">
+      <c r="AM6" s="9">
         <v>103</v>
       </c>
-      <c r="AM6" s="9">
+      <c r="AN6" s="9">
         <v>101</v>
       </c>
-      <c r="AN6" s="9">
+      <c r="AO6" s="9">
         <v>95</v>
       </c>
-      <c r="AO6" s="9">
+      <c r="AP6" s="9">
         <v>99</v>
       </c>
-      <c r="AP6" s="9">
+      <c r="AQ6" s="9">
         <v>103</v>
       </c>
-      <c r="AQ6" s="9">
+      <c r="AR6" s="9">
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>142</v>
       </c>
@@ -2919,102 +3041,105 @@
       <c r="K7" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="M7" s="2">
         <v>45039</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="N7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P7" s="9">
+      <c r="Q7" s="9">
         <v>76</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>0</v>
       </c>
       <c r="R7" s="9">
         <v>0</v>
       </c>
       <c r="S7" s="9">
+        <v>0</v>
+      </c>
+      <c r="T7" s="9">
         <v>1206</v>
       </c>
-      <c r="T7" s="10">
+      <c r="U7" s="10">
         <v>-0.11</v>
       </c>
-      <c r="U7" s="9">
+      <c r="V7" s="9">
         <v>40</v>
       </c>
-      <c r="V7" s="10">
+      <c r="W7" s="10">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="W7" s="9">
+      <c r="X7" s="9">
         <v>35</v>
       </c>
-      <c r="X7" s="9">
+      <c r="Y7" s="9">
         <v>106</v>
       </c>
-      <c r="Y7" s="9">
+      <c r="Z7" s="9">
         <v>103</v>
       </c>
-      <c r="Z7" s="9">
+      <c r="AA7" s="9">
         <v>107</v>
       </c>
-      <c r="AA7" s="9">
+      <c r="AB7" s="9">
         <v>183</v>
       </c>
-      <c r="AB7" s="9">
+      <c r="AC7" s="9">
         <v>107</v>
       </c>
-      <c r="AC7" s="9">
+      <c r="AD7" s="9">
         <v>98</v>
       </c>
-      <c r="AD7" s="9">
+      <c r="AE7" s="9">
         <v>107</v>
       </c>
-      <c r="AE7" s="9"/>
-      <c r="AF7" s="9">
+      <c r="AF7" s="9"/>
+      <c r="AG7" s="9">
         <v>6</v>
       </c>
-      <c r="AG7" s="9">
+      <c r="AH7" s="9">
         <v>271</v>
       </c>
-      <c r="AH7" s="9">
+      <c r="AI7" s="9">
         <v>304</v>
       </c>
-      <c r="AI7" s="9">
+      <c r="AJ7" s="9">
         <v>102</v>
       </c>
-      <c r="AJ7" s="9">
+      <c r="AK7" s="9">
         <v>5</v>
       </c>
-      <c r="AK7" s="9">
+      <c r="AL7" s="9">
         <v>106</v>
       </c>
-      <c r="AL7" s="9">
+      <c r="AM7" s="9">
         <v>108</v>
-      </c>
-      <c r="AM7" s="9">
-        <v>102</v>
       </c>
       <c r="AN7" s="9">
         <v>102</v>
       </c>
       <c r="AO7" s="9">
+        <v>102</v>
+      </c>
+      <c r="AP7" s="9">
         <v>100</v>
       </c>
-      <c r="AP7" s="9">
+      <c r="AQ7" s="9">
         <v>102</v>
       </c>
-      <c r="AQ7" s="9">
+      <c r="AR7" s="9">
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>153</v>
       </c>
@@ -3048,104 +3173,107 @@
       <c r="K8" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="M8" s="2">
         <v>44219</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="N8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="P8" s="9">
+      <c r="Q8" s="9">
         <v>80</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>0</v>
       </c>
       <c r="R8" s="9">
         <v>0</v>
       </c>
       <c r="S8" s="9">
+        <v>0</v>
+      </c>
+      <c r="T8" s="9">
         <v>1693</v>
       </c>
-      <c r="T8" s="10">
+      <c r="U8" s="10">
         <v>-0.1</v>
       </c>
-      <c r="U8" s="9">
+      <c r="V8" s="9">
         <v>62</v>
       </c>
-      <c r="V8" s="10">
+      <c r="W8" s="10">
         <v>0.1</v>
       </c>
-      <c r="W8" s="9">
+      <c r="X8" s="9">
         <v>71</v>
       </c>
-      <c r="X8" s="9">
+      <c r="Y8" s="9">
         <v>99</v>
       </c>
-      <c r="Y8" s="9">
+      <c r="Z8" s="9">
         <v>106</v>
       </c>
-      <c r="Z8" s="9">
+      <c r="AA8" s="9">
         <v>103</v>
       </c>
-      <c r="AA8" s="9">
+      <c r="AB8" s="9">
         <v>231</v>
       </c>
-      <c r="AB8" s="9">
+      <c r="AC8" s="9">
         <v>104</v>
-      </c>
-      <c r="AC8" s="9">
-        <v>100</v>
       </c>
       <c r="AD8" s="9">
         <v>100</v>
       </c>
       <c r="AE8" s="9">
+        <v>100</v>
+      </c>
+      <c r="AF8" s="9">
         <v>92</v>
       </c>
-      <c r="AF8" s="9">
+      <c r="AG8" s="9">
         <v>13</v>
       </c>
-      <c r="AG8" s="9">
+      <c r="AH8" s="9">
         <v>491</v>
       </c>
-      <c r="AH8" s="9">
+      <c r="AI8" s="9">
         <v>420</v>
       </c>
-      <c r="AI8" s="9">
+      <c r="AJ8" s="9">
         <v>107</v>
       </c>
-      <c r="AJ8" s="9">
+      <c r="AK8" s="9">
         <v>2</v>
       </c>
-      <c r="AK8" s="9">
+      <c r="AL8" s="9">
         <v>104</v>
       </c>
-      <c r="AL8" s="9">
+      <c r="AM8" s="9">
         <v>98</v>
       </c>
-      <c r="AM8" s="9">
+      <c r="AN8" s="9">
         <v>104</v>
-      </c>
-      <c r="AN8" s="9">
-        <v>101</v>
       </c>
       <c r="AO8" s="9">
         <v>101</v>
       </c>
       <c r="AP8" s="9">
+        <v>101</v>
+      </c>
+      <c r="AQ8" s="9">
         <v>102</v>
       </c>
-      <c r="AQ8" s="9">
+      <c r="AR8" s="9">
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>164</v>
       </c>
@@ -3179,104 +3307,107 @@
       <c r="K9" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="M9" s="2">
         <v>44287</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="N9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="P9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P9" s="9">
+      <c r="Q9" s="9">
         <v>81</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>0</v>
       </c>
       <c r="R9" s="9">
         <v>0</v>
       </c>
       <c r="S9" s="9">
+        <v>0</v>
+      </c>
+      <c r="T9" s="9">
         <v>1769</v>
       </c>
-      <c r="T9" s="10">
+      <c r="U9" s="10">
         <v>-0.16</v>
       </c>
-      <c r="U9" s="9">
+      <c r="V9" s="9">
         <v>58</v>
       </c>
-      <c r="V9" s="10">
+      <c r="W9" s="10">
         <v>-0.08</v>
       </c>
-      <c r="W9" s="9">
+      <c r="X9" s="9">
         <v>53</v>
       </c>
-      <c r="X9" s="9">
+      <c r="Y9" s="9">
         <v>99</v>
       </c>
-      <c r="Y9" s="9">
+      <c r="Z9" s="9">
         <v>102</v>
       </c>
-      <c r="Z9" s="9">
+      <c r="AA9" s="9">
         <v>101</v>
       </c>
-      <c r="AA9" s="9">
+      <c r="AB9" s="9">
         <v>264</v>
       </c>
-      <c r="AB9" s="9">
+      <c r="AC9" s="9">
         <v>108</v>
       </c>
-      <c r="AC9" s="9">
+      <c r="AD9" s="9">
         <v>99</v>
       </c>
-      <c r="AD9" s="9">
+      <c r="AE9" s="9">
         <v>101</v>
       </c>
-      <c r="AE9" s="9">
+      <c r="AF9" s="9">
         <v>97</v>
       </c>
-      <c r="AF9" s="9">
+      <c r="AG9" s="9">
         <v>16</v>
       </c>
-      <c r="AG9" s="9">
+      <c r="AH9" s="9">
         <v>402</v>
       </c>
-      <c r="AH9" s="9">
+      <c r="AI9" s="9">
         <v>653</v>
       </c>
-      <c r="AI9" s="9">
+      <c r="AJ9" s="9">
         <v>108</v>
       </c>
-      <c r="AJ9" s="9">
+      <c r="AK9" s="9">
         <v>5</v>
       </c>
-      <c r="AK9" s="9">
+      <c r="AL9" s="9">
         <v>109</v>
       </c>
-      <c r="AL9" s="9">
+      <c r="AM9" s="9">
         <v>105</v>
       </c>
-      <c r="AM9" s="9">
+      <c r="AN9" s="9">
         <v>104</v>
       </c>
-      <c r="AN9" s="9">
+      <c r="AO9" s="9">
         <v>103</v>
       </c>
-      <c r="AO9" s="9">
+      <c r="AP9" s="9">
         <v>101</v>
       </c>
-      <c r="AP9" s="9">
+      <c r="AQ9" s="9">
         <v>102</v>
       </c>
-      <c r="AQ9" s="9">
+      <c r="AR9" s="9">
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>175</v>
       </c>
@@ -3310,102 +3441,105 @@
       <c r="K10" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" s="2">
         <v>45026</v>
       </c>
-      <c r="M10" s="8" t="s">
+      <c r="N10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="P10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="P10" s="9">
+      <c r="Q10" s="9">
         <v>77</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>0</v>
       </c>
       <c r="R10" s="9">
         <v>0</v>
       </c>
       <c r="S10" s="9">
+        <v>0</v>
+      </c>
+      <c r="T10" s="9">
         <v>721</v>
       </c>
-      <c r="T10" s="10">
+      <c r="U10" s="10">
         <v>0.43</v>
       </c>
-      <c r="U10" s="9">
+      <c r="V10" s="9">
         <v>75</v>
       </c>
-      <c r="V10" s="10">
+      <c r="W10" s="10">
         <v>0.2</v>
       </c>
-      <c r="W10" s="9">
+      <c r="X10" s="9">
         <v>46</v>
       </c>
-      <c r="X10" s="9">
+      <c r="Y10" s="9">
         <v>102</v>
       </c>
-      <c r="Y10" s="9">
+      <c r="Z10" s="9">
         <v>106</v>
       </c>
-      <c r="Z10" s="9">
+      <c r="AA10" s="9">
         <v>105</v>
       </c>
-      <c r="AA10" s="9">
+      <c r="AB10" s="9">
         <v>260</v>
       </c>
-      <c r="AB10" s="9">
+      <c r="AC10" s="9">
         <v>105</v>
       </c>
-      <c r="AC10" s="9">
+      <c r="AD10" s="9">
         <v>100</v>
       </c>
-      <c r="AD10" s="9">
+      <c r="AE10" s="9">
         <v>107</v>
       </c>
-      <c r="AE10" s="9"/>
-      <c r="AF10" s="9">
+      <c r="AF10" s="9"/>
+      <c r="AG10" s="9">
         <v>10</v>
       </c>
-      <c r="AG10" s="9">
+      <c r="AH10" s="9">
         <v>423</v>
       </c>
-      <c r="AH10" s="9">
+      <c r="AI10" s="9">
         <v>520</v>
       </c>
-      <c r="AI10" s="9">
+      <c r="AJ10" s="9">
         <v>104</v>
       </c>
-      <c r="AJ10" s="9">
+      <c r="AK10" s="9">
         <v>5</v>
       </c>
-      <c r="AK10" s="9">
+      <c r="AL10" s="9">
         <v>105</v>
       </c>
-      <c r="AL10" s="9">
+      <c r="AM10" s="9">
         <v>104</v>
       </c>
-      <c r="AM10" s="9">
+      <c r="AN10" s="9">
         <v>103</v>
       </c>
-      <c r="AN10" s="9">
+      <c r="AO10" s="9">
         <v>104</v>
       </c>
-      <c r="AO10" s="9">
+      <c r="AP10" s="9">
         <v>103</v>
       </c>
-      <c r="AP10" s="9">
+      <c r="AQ10" s="9">
         <v>102</v>
       </c>
-      <c r="AQ10" s="9">
+      <c r="AR10" s="9">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>186</v>
       </c>
@@ -3439,102 +3573,105 @@
       <c r="K11" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="16" t="s">
+        <v>540</v>
+      </c>
+      <c r="M11" s="2">
         <v>45140</v>
       </c>
-      <c r="M11" s="8" t="s">
+      <c r="N11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="O11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="P11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P11" s="9">
+      <c r="Q11" s="9">
         <v>76</v>
-      </c>
-      <c r="Q11" s="9">
-        <v>0</v>
       </c>
       <c r="R11" s="9">
         <v>0</v>
       </c>
       <c r="S11" s="9">
+        <v>0</v>
+      </c>
+      <c r="T11" s="9">
         <v>1035</v>
       </c>
-      <c r="T11" s="10">
+      <c r="U11" s="10">
         <v>0.03</v>
       </c>
-      <c r="U11" s="9">
+      <c r="V11" s="9">
         <v>48</v>
       </c>
-      <c r="V11" s="10">
+      <c r="W11" s="10">
         <v>0.09</v>
       </c>
-      <c r="W11" s="9">
+      <c r="X11" s="9">
         <v>46</v>
       </c>
-      <c r="X11" s="9">
+      <c r="Y11" s="9">
         <v>104</v>
       </c>
-      <c r="Y11" s="9">
+      <c r="Z11" s="9">
         <v>111</v>
       </c>
-      <c r="Z11" s="9">
+      <c r="AA11" s="9">
         <v>108</v>
       </c>
-      <c r="AA11" s="9">
+      <c r="AB11" s="9">
         <v>296</v>
       </c>
-      <c r="AB11" s="9">
+      <c r="AC11" s="9">
         <v>105</v>
       </c>
-      <c r="AC11" s="9">
+      <c r="AD11" s="9">
         <v>100</v>
       </c>
-      <c r="AD11" s="9">
+      <c r="AE11" s="9">
         <v>105</v>
       </c>
-      <c r="AE11" s="9"/>
-      <c r="AF11" s="9">
+      <c r="AF11" s="9"/>
+      <c r="AG11" s="9">
         <v>14</v>
       </c>
-      <c r="AG11" s="9">
+      <c r="AH11" s="9">
         <v>342</v>
       </c>
-      <c r="AH11" s="9">
+      <c r="AI11" s="9">
         <v>1004</v>
       </c>
-      <c r="AI11" s="9">
+      <c r="AJ11" s="9">
         <v>106</v>
       </c>
-      <c r="AJ11" s="9">
+      <c r="AK11" s="9">
         <v>5</v>
       </c>
-      <c r="AK11" s="9">
+      <c r="AL11" s="9">
         <v>106</v>
       </c>
-      <c r="AL11" s="9">
+      <c r="AM11" s="9">
         <v>107</v>
-      </c>
-      <c r="AM11" s="9">
-        <v>103</v>
       </c>
       <c r="AN11" s="9">
         <v>103</v>
       </c>
       <c r="AO11" s="9">
+        <v>103</v>
+      </c>
+      <c r="AP11" s="9">
         <v>102</v>
       </c>
-      <c r="AP11" s="9">
+      <c r="AQ11" s="9">
         <v>99</v>
       </c>
-      <c r="AQ11" s="9">
+      <c r="AR11" s="9">
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>409</v>
       </c>
@@ -3568,102 +3705,105 @@
       <c r="K12" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="M12" s="2">
         <v>45201</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="N12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="O12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O12" s="2" t="s">
+      <c r="P12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="9">
+      <c r="Q12" s="9">
         <v>75</v>
-      </c>
-      <c r="Q12" s="9">
-        <v>0</v>
       </c>
       <c r="R12" s="9">
         <v>0</v>
       </c>
       <c r="S12" s="9">
+        <v>0</v>
+      </c>
+      <c r="T12" s="9">
         <v>2519</v>
       </c>
-      <c r="T12" s="10">
+      <c r="U12" s="10">
         <v>-0.33</v>
       </c>
-      <c r="U12" s="9">
+      <c r="V12" s="9">
         <v>69</v>
       </c>
-      <c r="V12" s="10">
+      <c r="W12" s="10">
         <v>-0.11</v>
       </c>
-      <c r="W12" s="9">
+      <c r="X12" s="9">
         <v>76</v>
       </c>
-      <c r="X12" s="9">
+      <c r="Y12" s="9">
         <v>104</v>
       </c>
-      <c r="Y12" s="9">
+      <c r="Z12" s="9">
         <v>103</v>
       </c>
-      <c r="Z12" s="9">
+      <c r="AA12" s="9">
         <v>105</v>
       </c>
-      <c r="AA12" s="9">
+      <c r="AB12" s="9">
         <v>344</v>
       </c>
-      <c r="AB12" s="9">
+      <c r="AC12" s="9">
         <v>108</v>
-      </c>
-      <c r="AC12" s="9">
-        <v>100</v>
       </c>
       <c r="AD12" s="9">
         <v>100</v>
       </c>
-      <c r="AE12" s="9"/>
-      <c r="AF12" s="9">
+      <c r="AE12" s="9">
+        <v>100</v>
+      </c>
+      <c r="AF12" s="9"/>
+      <c r="AG12" s="9">
         <v>18</v>
       </c>
-      <c r="AG12" s="9">
+      <c r="AH12" s="9">
         <v>534</v>
       </c>
-      <c r="AH12" s="9">
+      <c r="AI12" s="9">
         <v>698</v>
       </c>
-      <c r="AI12" s="9">
+      <c r="AJ12" s="9">
         <v>110</v>
       </c>
-      <c r="AJ12" s="9">
+      <c r="AK12" s="9">
         <v>7</v>
-      </c>
-      <c r="AK12" s="9">
-        <v>107</v>
       </c>
       <c r="AL12" s="9">
         <v>107</v>
       </c>
       <c r="AM12" s="9">
+        <v>107</v>
+      </c>
+      <c r="AN12" s="9">
         <v>102</v>
       </c>
-      <c r="AN12" s="9">
+      <c r="AO12" s="9">
         <v>104</v>
       </c>
-      <c r="AO12" s="9">
+      <c r="AP12" s="9">
         <v>103</v>
       </c>
-      <c r="AP12" s="9">
+      <c r="AQ12" s="9">
         <v>97</v>
       </c>
-      <c r="AQ12" s="9">
+      <c r="AR12" s="9">
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>197</v>
       </c>
@@ -3697,104 +3837,107 @@
       <c r="K13" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="M13" s="2">
         <v>42145</v>
       </c>
-      <c r="M13" s="8" t="s">
+      <c r="N13" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="O13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="P13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P13" s="9">
+      <c r="Q13" s="9">
         <v>99</v>
       </c>
-      <c r="Q13" s="9">
+      <c r="R13" s="9">
         <v>8118</v>
       </c>
-      <c r="R13" s="9">
+      <c r="S13" s="9">
         <v>2223</v>
       </c>
-      <c r="S13" s="9">
+      <c r="T13" s="9">
         <v>711</v>
       </c>
-      <c r="T13" s="10">
+      <c r="U13" s="10">
         <v>-0.13</v>
       </c>
-      <c r="U13" s="9">
+      <c r="V13" s="9">
         <v>17</v>
       </c>
-      <c r="V13" s="10">
+      <c r="W13" s="10">
         <v>-0.12</v>
       </c>
-      <c r="W13" s="9">
+      <c r="X13" s="9">
         <v>13</v>
       </c>
-      <c r="X13" s="9">
+      <c r="Y13" s="9">
         <v>96</v>
       </c>
-      <c r="Y13" s="9">
+      <c r="Z13" s="9">
         <v>100</v>
       </c>
-      <c r="Z13" s="9">
+      <c r="AA13" s="9">
         <v>97</v>
       </c>
-      <c r="AA13" s="9">
+      <c r="AB13" s="9">
         <v>130</v>
       </c>
-      <c r="AB13" s="9">
+      <c r="AC13" s="9">
         <v>100</v>
       </c>
-      <c r="AC13" s="9">
+      <c r="AD13" s="9">
         <v>101</v>
       </c>
-      <c r="AD13" s="9">
+      <c r="AE13" s="9">
         <v>97</v>
       </c>
-      <c r="AE13" s="9">
+      <c r="AF13" s="9">
         <v>87</v>
       </c>
-      <c r="AF13" s="9">
+      <c r="AG13" s="9">
         <v>10</v>
       </c>
-      <c r="AG13" s="9">
+      <c r="AH13" s="9">
         <v>107</v>
       </c>
-      <c r="AH13" s="9">
+      <c r="AI13" s="9">
         <v>470</v>
       </c>
-      <c r="AI13" s="9">
+      <c r="AJ13" s="9">
         <v>106</v>
       </c>
-      <c r="AJ13" s="9">
+      <c r="AK13" s="9">
         <v>1</v>
       </c>
-      <c r="AK13" s="9">
+      <c r="AL13" s="9">
         <v>102</v>
       </c>
-      <c r="AL13" s="9">
+      <c r="AM13" s="9">
         <v>97</v>
       </c>
-      <c r="AM13" s="9">
+      <c r="AN13" s="9">
         <v>96</v>
       </c>
-      <c r="AN13" s="9">
+      <c r="AO13" s="9">
         <v>101</v>
       </c>
-      <c r="AO13" s="9">
+      <c r="AP13" s="9">
         <v>107</v>
       </c>
-      <c r="AP13" s="9">
+      <c r="AQ13" s="9">
         <v>103</v>
       </c>
-      <c r="AQ13" s="9">
+      <c r="AR13" s="9">
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>208</v>
       </c>
@@ -3828,102 +3971,105 @@
       <c r="K14" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="M14" s="2">
         <v>44307</v>
       </c>
-      <c r="M14" s="8" t="s">
+      <c r="N14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="O14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="P14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P14" s="9">
+      <c r="Q14" s="9">
         <v>88</v>
       </c>
-      <c r="Q14" s="9">
+      <c r="R14" s="9">
         <v>163</v>
       </c>
-      <c r="R14" s="9">
+      <c r="S14" s="9">
         <v>88</v>
       </c>
-      <c r="S14" s="9">
+      <c r="T14" s="9">
         <v>1192</v>
       </c>
-      <c r="T14" s="10">
+      <c r="U14" s="10">
         <v>-0.1</v>
       </c>
-      <c r="U14" s="9">
+      <c r="V14" s="9">
         <v>40</v>
       </c>
-      <c r="V14" s="10">
+      <c r="W14" s="10">
         <v>0.1</v>
       </c>
-      <c r="W14" s="9">
+      <c r="X14" s="9">
         <v>53</v>
       </c>
-      <c r="X14" s="9">
+      <c r="Y14" s="9">
         <v>100</v>
       </c>
-      <c r="Y14" s="9">
+      <c r="Z14" s="9">
         <v>101</v>
       </c>
-      <c r="Z14" s="9">
+      <c r="AA14" s="9">
         <v>100</v>
       </c>
-      <c r="AA14" s="9">
+      <c r="AB14" s="9">
         <v>223</v>
       </c>
-      <c r="AB14" s="9">
+      <c r="AC14" s="9">
         <v>103</v>
       </c>
-      <c r="AC14" s="9">
+      <c r="AD14" s="9">
         <v>96</v>
       </c>
-      <c r="AD14" s="9">
+      <c r="AE14" s="9">
         <v>103</v>
       </c>
-      <c r="AE14" s="9"/>
-      <c r="AF14" s="9">
+      <c r="AF14" s="9"/>
+      <c r="AG14" s="9">
         <v>13</v>
       </c>
-      <c r="AG14" s="9">
+      <c r="AH14" s="9">
         <v>348</v>
       </c>
-      <c r="AH14" s="9">
+      <c r="AI14" s="9">
         <v>200</v>
       </c>
-      <c r="AI14" s="9">
+      <c r="AJ14" s="9">
         <v>109</v>
       </c>
-      <c r="AJ14" s="9">
+      <c r="AK14" s="9">
         <v>5</v>
       </c>
-      <c r="AK14" s="9">
+      <c r="AL14" s="9">
         <v>103</v>
       </c>
-      <c r="AL14" s="9">
+      <c r="AM14" s="9">
         <v>110</v>
       </c>
-      <c r="AM14" s="9">
+      <c r="AN14" s="9">
         <v>98</v>
       </c>
-      <c r="AN14" s="9">
+      <c r="AO14" s="9">
         <v>100</v>
       </c>
-      <c r="AO14" s="9">
+      <c r="AP14" s="9">
         <v>104</v>
       </c>
-      <c r="AP14" s="9">
+      <c r="AQ14" s="9">
         <v>101</v>
       </c>
-      <c r="AQ14" s="9">
+      <c r="AR14" s="9">
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>420</v>
       </c>
@@ -3957,102 +4103,105 @@
       <c r="K15" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="L15" s="2">
+      <c r="L15" s="16" t="s">
+        <v>540</v>
+      </c>
+      <c r="M15" s="2">
         <v>45403</v>
       </c>
-      <c r="M15" s="8" t="s">
+      <c r="N15" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="O15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="P15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P15" s="9">
+      <c r="Q15" s="9">
         <v>76</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>0</v>
       </c>
       <c r="R15" s="9">
         <v>0</v>
       </c>
       <c r="S15" s="9">
+        <v>0</v>
+      </c>
+      <c r="T15" s="9">
         <v>1147</v>
       </c>
-      <c r="T15" s="10">
+      <c r="U15" s="10">
         <v>-0.3</v>
       </c>
-      <c r="U15" s="9">
+      <c r="V15" s="9">
         <v>17</v>
       </c>
-      <c r="V15" s="10">
+      <c r="W15" s="10">
         <v>0.01</v>
       </c>
-      <c r="W15" s="9">
+      <c r="X15" s="9">
         <v>41</v>
       </c>
-      <c r="X15" s="9">
+      <c r="Y15" s="9">
         <v>104</v>
-      </c>
-      <c r="Y15" s="9">
-        <v>107</v>
       </c>
       <c r="Z15" s="9">
         <v>107</v>
       </c>
       <c r="AA15" s="9">
+        <v>107</v>
+      </c>
+      <c r="AB15" s="9">
         <v>321</v>
       </c>
-      <c r="AB15" s="9">
+      <c r="AC15" s="9">
         <v>110</v>
       </c>
-      <c r="AC15" s="9">
+      <c r="AD15" s="9">
         <v>99</v>
       </c>
-      <c r="AD15" s="9">
+      <c r="AE15" s="9">
         <v>103</v>
       </c>
-      <c r="AE15" s="9"/>
-      <c r="AF15" s="9">
+      <c r="AF15" s="9"/>
+      <c r="AG15" s="9">
         <v>16</v>
       </c>
-      <c r="AG15" s="9">
+      <c r="AH15" s="9">
         <v>227</v>
       </c>
-      <c r="AH15" s="9">
+      <c r="AI15" s="9">
         <v>1078</v>
       </c>
-      <c r="AI15" s="9">
+      <c r="AJ15" s="9">
         <v>109</v>
       </c>
-      <c r="AJ15" s="9">
+      <c r="AK15" s="9">
         <v>8</v>
       </c>
-      <c r="AK15" s="9">
+      <c r="AL15" s="9">
         <v>111</v>
       </c>
-      <c r="AL15" s="9">
+      <c r="AM15" s="9">
         <v>106</v>
       </c>
-      <c r="AM15" s="9">
+      <c r="AN15" s="9">
         <v>105</v>
       </c>
-      <c r="AN15" s="9">
+      <c r="AO15" s="9">
         <v>103</v>
       </c>
-      <c r="AO15" s="9">
+      <c r="AP15" s="9">
         <v>105</v>
       </c>
-      <c r="AP15" s="9">
+      <c r="AQ15" s="9">
         <v>98</v>
       </c>
-      <c r="AQ15" s="9">
+      <c r="AR15" s="9">
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>426</v>
       </c>
@@ -4086,102 +4235,105 @@
       <c r="K16" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="M16" s="2">
         <v>45341</v>
       </c>
-      <c r="M16" s="8" t="s">
+      <c r="N16" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="O16" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="P16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="P16" s="9">
+      <c r="Q16" s="9">
         <v>76</v>
-      </c>
-      <c r="Q16" s="9">
-        <v>0</v>
       </c>
       <c r="R16" s="9">
         <v>0</v>
       </c>
       <c r="S16" s="9">
+        <v>0</v>
+      </c>
+      <c r="T16" s="9">
         <v>1435</v>
       </c>
-      <c r="T16" s="10">
+      <c r="U16" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="U16" s="9">
+      <c r="V16" s="9">
         <v>69</v>
       </c>
-      <c r="V16" s="10">
+      <c r="W16" s="10">
         <v>0.21</v>
       </c>
-      <c r="W16" s="9">
+      <c r="X16" s="9">
         <v>74</v>
       </c>
-      <c r="X16" s="9">
+      <c r="Y16" s="9">
         <v>106</v>
       </c>
-      <c r="Y16" s="9">
+      <c r="Z16" s="9">
         <v>105</v>
       </c>
-      <c r="Z16" s="9">
+      <c r="AA16" s="9">
         <v>107</v>
       </c>
-      <c r="AA16" s="9">
+      <c r="AB16" s="9">
         <v>296</v>
       </c>
-      <c r="AB16" s="9">
+      <c r="AC16" s="9">
         <v>104</v>
       </c>
-      <c r="AC16" s="9">
+      <c r="AD16" s="9">
         <v>100</v>
       </c>
-      <c r="AD16" s="9">
+      <c r="AE16" s="9">
         <v>102</v>
       </c>
-      <c r="AE16" s="9"/>
-      <c r="AF16" s="9">
+      <c r="AF16" s="9"/>
+      <c r="AG16" s="9">
         <v>15</v>
       </c>
-      <c r="AG16" s="9">
+      <c r="AH16" s="9">
         <v>525</v>
       </c>
-      <c r="AH16" s="9">
+      <c r="AI16" s="9">
         <v>443</v>
       </c>
-      <c r="AI16" s="9">
+      <c r="AJ16" s="9">
         <v>108</v>
       </c>
-      <c r="AJ16" s="9">
+      <c r="AK16" s="9">
         <v>5</v>
       </c>
-      <c r="AK16" s="9">
+      <c r="AL16" s="9">
         <v>101</v>
       </c>
-      <c r="AL16" s="9">
+      <c r="AM16" s="9">
         <v>108</v>
       </c>
-      <c r="AM16" s="9">
+      <c r="AN16" s="9">
         <v>107</v>
       </c>
-      <c r="AN16" s="9">
+      <c r="AO16" s="9">
         <v>100</v>
       </c>
-      <c r="AO16" s="9">
+      <c r="AP16" s="9">
         <v>103</v>
       </c>
-      <c r="AP16" s="9">
+      <c r="AQ16" s="9">
         <v>97</v>
       </c>
-      <c r="AQ16" s="9">
+      <c r="AR16" s="9">
         <v>107</v>
       </c>
     </row>
-    <row r="17" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>431</v>
       </c>
@@ -4215,102 +4367,105 @@
       <c r="K17" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="L17" s="2">
+      <c r="L17" s="16" t="s">
+        <v>543</v>
+      </c>
+      <c r="M17" s="2">
         <v>45412</v>
       </c>
-      <c r="M17" s="8" t="s">
+      <c r="N17" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="O17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="P17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P17" s="9">
+      <c r="Q17" s="9">
         <v>75</v>
-      </c>
-      <c r="Q17" s="9">
-        <v>0</v>
       </c>
       <c r="R17" s="9">
         <v>0</v>
       </c>
       <c r="S17" s="9">
+        <v>0</v>
+      </c>
+      <c r="T17" s="9">
         <v>1861</v>
       </c>
-      <c r="T17" s="10">
+      <c r="U17" s="10">
         <v>-0.35</v>
       </c>
-      <c r="U17" s="9">
+      <c r="V17" s="9">
         <v>40</v>
       </c>
-      <c r="V17" s="10">
+      <c r="W17" s="10">
         <v>-0.11</v>
       </c>
-      <c r="W17" s="9">
+      <c r="X17" s="9">
         <v>53</v>
       </c>
-      <c r="X17" s="9">
+      <c r="Y17" s="9">
         <v>101</v>
       </c>
-      <c r="Y17" s="9">
+      <c r="Z17" s="9">
         <v>104</v>
       </c>
-      <c r="Z17" s="9">
+      <c r="AA17" s="9">
         <v>102</v>
       </c>
-      <c r="AA17" s="9">
+      <c r="AB17" s="9">
         <v>331</v>
       </c>
-      <c r="AB17" s="9">
+      <c r="AC17" s="9">
         <v>108</v>
       </c>
-      <c r="AC17" s="9">
+      <c r="AD17" s="9">
         <v>100</v>
       </c>
-      <c r="AD17" s="9">
+      <c r="AE17" s="9">
         <v>103</v>
       </c>
-      <c r="AE17" s="9"/>
-      <c r="AF17" s="9">
+      <c r="AF17" s="9"/>
+      <c r="AG17" s="9">
         <v>15</v>
       </c>
-      <c r="AG17" s="9">
+      <c r="AH17" s="9">
         <v>348</v>
       </c>
-      <c r="AH17" s="9">
+      <c r="AI17" s="9">
         <v>1194</v>
       </c>
-      <c r="AI17" s="9">
+      <c r="AJ17" s="9">
         <v>106</v>
       </c>
-      <c r="AJ17" s="9">
+      <c r="AK17" s="9">
         <v>8</v>
       </c>
-      <c r="AK17" s="9">
+      <c r="AL17" s="9">
         <v>109</v>
       </c>
-      <c r="AL17" s="9">
+      <c r="AM17" s="9">
         <v>111</v>
       </c>
-      <c r="AM17" s="9">
+      <c r="AN17" s="9">
         <v>100</v>
       </c>
-      <c r="AN17" s="9">
+      <c r="AO17" s="9">
         <v>107</v>
       </c>
-      <c r="AO17" s="9">
+      <c r="AP17" s="9">
         <v>105</v>
       </c>
-      <c r="AP17" s="9">
+      <c r="AQ17" s="9">
         <v>101</v>
       </c>
-      <c r="AQ17" s="9">
+      <c r="AR17" s="9">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>442</v>
       </c>
@@ -4344,56 +4499,56 @@
       <c r="K18" s="12" t="s">
         <v>452</v>
       </c>
-      <c r="L18" s="2">
+      <c r="L18" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="M18" s="2">
         <v>45383</v>
       </c>
-      <c r="M18" s="8" t="s">
+      <c r="N18" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="O18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="P18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P18" s="9">
+      <c r="Q18" s="9">
         <v>74</v>
-      </c>
-      <c r="Q18" s="9">
-        <v>0</v>
       </c>
       <c r="R18" s="9">
         <v>0</v>
       </c>
       <c r="S18" s="9">
+        <v>0</v>
+      </c>
+      <c r="T18" s="9">
         <v>2345</v>
       </c>
-      <c r="T18" s="10">
+      <c r="U18" s="10">
         <v>-0.28000000000000003</v>
       </c>
-      <c r="U18" s="9">
+      <c r="V18" s="9">
         <v>68</v>
       </c>
-      <c r="V18" s="10">
+      <c r="W18" s="10">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="W18" s="9">
+      <c r="X18" s="9">
         <v>74</v>
       </c>
-      <c r="X18" s="9">
+      <c r="Y18" s="9">
         <v>102</v>
-      </c>
-      <c r="Y18" s="9">
-        <v>103</v>
       </c>
       <c r="Z18" s="9">
         <v>103</v>
       </c>
       <c r="AA18" s="9">
+        <v>103</v>
+      </c>
+      <c r="AB18" s="9">
         <v>283</v>
-      </c>
-      <c r="AB18" s="9">
-        <v>100</v>
       </c>
       <c r="AC18" s="9">
         <v>100</v>
@@ -4401,45 +4556,48 @@
       <c r="AD18" s="9">
         <v>100</v>
       </c>
-      <c r="AE18" s="9"/>
-      <c r="AF18" s="9">
+      <c r="AE18" s="9">
+        <v>100</v>
+      </c>
+      <c r="AF18" s="9"/>
+      <c r="AG18" s="9">
         <v>15</v>
       </c>
-      <c r="AG18" s="9">
+      <c r="AH18" s="9">
         <v>522</v>
       </c>
-      <c r="AH18" s="9">
+      <c r="AI18" s="9">
         <v>676</v>
       </c>
-      <c r="AI18" s="9">
+      <c r="AJ18" s="9">
         <v>106</v>
       </c>
-      <c r="AJ18" s="9">
+      <c r="AK18" s="9">
         <v>6</v>
       </c>
-      <c r="AK18" s="9">
+      <c r="AL18" s="9">
         <v>100</v>
       </c>
-      <c r="AL18" s="9">
+      <c r="AM18" s="9">
         <v>106</v>
       </c>
-      <c r="AM18" s="9">
+      <c r="AN18" s="9">
         <v>108</v>
-      </c>
-      <c r="AN18" s="9">
-        <v>104</v>
       </c>
       <c r="AO18" s="9">
         <v>104</v>
       </c>
       <c r="AP18" s="9">
+        <v>104</v>
+      </c>
+      <c r="AQ18" s="9">
         <v>96</v>
       </c>
-      <c r="AQ18" s="9">
+      <c r="AR18" s="9">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>453</v>
       </c>
@@ -4473,102 +4631,105 @@
       <c r="K19" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="L19" s="2">
+      <c r="L19" s="16" t="s">
+        <v>545</v>
+      </c>
+      <c r="M19" s="2">
         <v>45328</v>
       </c>
-      <c r="M19" s="8" t="s">
+      <c r="N19" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="O19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O19" s="2" t="s">
+      <c r="P19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P19" s="9">
+      <c r="Q19" s="9">
         <v>76</v>
-      </c>
-      <c r="Q19" s="9">
-        <v>0</v>
       </c>
       <c r="R19" s="9">
         <v>0</v>
       </c>
       <c r="S19" s="9">
+        <v>0</v>
+      </c>
+      <c r="T19" s="9">
         <v>1781</v>
       </c>
-      <c r="T19" s="10">
+      <c r="U19" s="10">
         <v>-0.01</v>
       </c>
-      <c r="U19" s="9">
+      <c r="V19" s="9">
         <v>76</v>
       </c>
-      <c r="V19" s="10">
+      <c r="W19" s="10">
         <v>-0.02</v>
       </c>
-      <c r="W19" s="9">
+      <c r="X19" s="9">
         <v>60</v>
-      </c>
-      <c r="X19" s="9">
-        <v>107</v>
       </c>
       <c r="Y19" s="9">
         <v>107</v>
       </c>
       <c r="Z19" s="9">
+        <v>107</v>
+      </c>
+      <c r="AA19" s="9">
         <v>108</v>
       </c>
-      <c r="AA19" s="9">
+      <c r="AB19" s="9">
         <v>363</v>
       </c>
-      <c r="AB19" s="9">
+      <c r="AC19" s="9">
         <v>104</v>
       </c>
-      <c r="AC19" s="9">
+      <c r="AD19" s="9">
         <v>99</v>
       </c>
-      <c r="AD19" s="9">
+      <c r="AE19" s="9">
         <v>96</v>
       </c>
-      <c r="AE19" s="9"/>
-      <c r="AF19" s="9">
+      <c r="AF19" s="9"/>
+      <c r="AG19" s="9">
         <v>21</v>
       </c>
-      <c r="AG19" s="9">
+      <c r="AH19" s="9">
         <v>486</v>
       </c>
-      <c r="AH19" s="9">
+      <c r="AI19" s="9">
         <v>1035</v>
       </c>
-      <c r="AI19" s="9">
+      <c r="AJ19" s="9">
         <v>112</v>
       </c>
-      <c r="AJ19" s="9">
+      <c r="AK19" s="9">
         <v>5</v>
       </c>
-      <c r="AK19" s="9">
+      <c r="AL19" s="9">
         <v>104</v>
       </c>
-      <c r="AL19" s="9">
+      <c r="AM19" s="9">
         <v>111</v>
       </c>
-      <c r="AM19" s="9">
+      <c r="AN19" s="9">
         <v>100</v>
       </c>
-      <c r="AN19" s="9">
+      <c r="AO19" s="9">
         <v>101</v>
-      </c>
-      <c r="AO19" s="9">
-        <v>103</v>
       </c>
       <c r="AP19" s="9">
         <v>103</v>
       </c>
       <c r="AQ19" s="9">
+        <v>103</v>
+      </c>
+      <c r="AR19" s="9">
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>461</v>
       </c>
@@ -4602,102 +4763,105 @@
       <c r="K20" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="L20" s="2">
+      <c r="L20" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="M20" s="2">
         <v>45112</v>
       </c>
-      <c r="M20" s="8" t="s">
+      <c r="N20" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="O20" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O20" s="2" t="s">
+      <c r="P20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="P20" s="9">
+      <c r="Q20" s="9">
         <v>77</v>
-      </c>
-      <c r="Q20" s="9">
-        <v>0</v>
       </c>
       <c r="R20" s="9">
         <v>0</v>
       </c>
       <c r="S20" s="9">
+        <v>0</v>
+      </c>
+      <c r="T20" s="9">
         <v>1624</v>
       </c>
-      <c r="T20" s="10">
+      <c r="U20" s="10">
         <v>-0.25</v>
       </c>
-      <c r="U20" s="9">
+      <c r="V20" s="9">
         <v>42</v>
       </c>
-      <c r="V20" s="10">
+      <c r="W20" s="10">
         <v>0.06</v>
       </c>
-      <c r="W20" s="9">
+      <c r="X20" s="9">
         <v>64</v>
       </c>
-      <c r="X20" s="9">
+      <c r="Y20" s="9">
         <v>105</v>
       </c>
-      <c r="Y20" s="9">
+      <c r="Z20" s="9">
         <v>106</v>
       </c>
-      <c r="Z20" s="9">
+      <c r="AA20" s="9">
         <v>107</v>
       </c>
-      <c r="AA20" s="9">
+      <c r="AB20" s="9">
         <v>264</v>
       </c>
-      <c r="AB20" s="9">
+      <c r="AC20" s="9">
         <v>99</v>
       </c>
-      <c r="AC20" s="9">
+      <c r="AD20" s="9">
         <v>104</v>
       </c>
-      <c r="AD20" s="9">
+      <c r="AE20" s="9">
         <v>105</v>
       </c>
-      <c r="AE20" s="9"/>
-      <c r="AF20" s="9">
+      <c r="AF20" s="9"/>
+      <c r="AG20" s="9">
         <v>13</v>
       </c>
-      <c r="AG20" s="9">
+      <c r="AH20" s="9">
         <v>401</v>
       </c>
-      <c r="AH20" s="9">
+      <c r="AI20" s="9">
         <v>368</v>
       </c>
-      <c r="AI20" s="9">
+      <c r="AJ20" s="9">
         <v>107</v>
       </c>
-      <c r="AJ20" s="9">
+      <c r="AK20" s="9">
         <v>7</v>
       </c>
-      <c r="AK20" s="9">
+      <c r="AL20" s="9">
         <v>100</v>
       </c>
-      <c r="AL20" s="9">
+      <c r="AM20" s="9">
         <v>110</v>
       </c>
-      <c r="AM20" s="9">
+      <c r="AN20" s="9">
         <v>103</v>
       </c>
-      <c r="AN20" s="9">
+      <c r="AO20" s="9">
         <v>106</v>
       </c>
-      <c r="AO20" s="9">
+      <c r="AP20" s="9">
         <v>105</v>
       </c>
-      <c r="AP20" s="9">
+      <c r="AQ20" s="9">
         <v>99</v>
       </c>
-      <c r="AQ20" s="9">
+      <c r="AR20" s="9">
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>466</v>
       </c>
@@ -4731,102 +4895,105 @@
       <c r="K21" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="L21" s="2">
+      <c r="L21" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="M21" s="2">
         <v>45222</v>
       </c>
-      <c r="M21" s="8" t="s">
+      <c r="N21" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="O21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O21" s="2" t="s">
+      <c r="P21" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P21" s="9">
+      <c r="Q21" s="9">
         <v>77</v>
-      </c>
-      <c r="Q21" s="9">
-        <v>0</v>
       </c>
       <c r="R21" s="9">
         <v>0</v>
       </c>
       <c r="S21" s="9">
+        <v>0</v>
+      </c>
+      <c r="T21" s="9">
         <v>1821</v>
       </c>
-      <c r="T21" s="10">
+      <c r="U21" s="10">
         <v>-0.28000000000000003</v>
       </c>
-      <c r="U21" s="9">
+      <c r="V21" s="9">
         <v>46</v>
       </c>
-      <c r="V21" s="10">
+      <c r="W21" s="10">
         <v>0.04</v>
       </c>
-      <c r="W21" s="9">
+      <c r="X21" s="9">
         <v>69</v>
       </c>
-      <c r="X21" s="9">
+      <c r="Y21" s="9">
         <v>100</v>
       </c>
-      <c r="Y21" s="9">
+      <c r="Z21" s="9">
         <v>107</v>
       </c>
-      <c r="Z21" s="9">
+      <c r="AA21" s="9">
         <v>106</v>
       </c>
-      <c r="AA21" s="9">
+      <c r="AB21" s="9">
         <v>298</v>
       </c>
-      <c r="AB21" s="9">
+      <c r="AC21" s="9">
         <v>107</v>
-      </c>
-      <c r="AC21" s="9">
-        <v>99</v>
       </c>
       <c r="AD21" s="9">
         <v>99</v>
       </c>
-      <c r="AE21" s="9"/>
-      <c r="AF21" s="9">
+      <c r="AE21" s="9">
+        <v>99</v>
+      </c>
+      <c r="AF21" s="9"/>
+      <c r="AG21" s="9">
         <v>15</v>
       </c>
-      <c r="AG21" s="9">
+      <c r="AH21" s="9">
         <v>435</v>
       </c>
-      <c r="AH21" s="9">
+      <c r="AI21" s="9">
         <v>581</v>
       </c>
-      <c r="AI21" s="9">
+      <c r="AJ21" s="9">
         <v>108</v>
       </c>
-      <c r="AJ21" s="9">
+      <c r="AK21" s="9">
         <v>7</v>
       </c>
-      <c r="AK21" s="9">
+      <c r="AL21" s="9">
         <v>106</v>
       </c>
-      <c r="AL21" s="9">
+      <c r="AM21" s="9">
         <v>104</v>
       </c>
-      <c r="AM21" s="9">
+      <c r="AN21" s="9">
         <v>107</v>
-      </c>
-      <c r="AN21" s="9">
-        <v>105</v>
       </c>
       <c r="AO21" s="9">
         <v>105</v>
       </c>
       <c r="AP21" s="9">
+        <v>105</v>
+      </c>
+      <c r="AQ21" s="9">
         <v>101</v>
       </c>
-      <c r="AQ21" s="9">
+      <c r="AR21" s="9">
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
         <v>471</v>
       </c>
@@ -4860,102 +5027,105 @@
       <c r="K22" s="13" t="s">
         <v>478</v>
       </c>
-      <c r="L22" s="2">
+      <c r="L22" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="M22" s="2">
         <v>44923</v>
       </c>
-      <c r="M22" s="8" t="s">
+      <c r="N22" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="O22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O22" s="2" t="s">
+      <c r="P22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="P22" s="9">
+      <c r="Q22" s="9">
         <v>78</v>
-      </c>
-      <c r="Q22" s="9">
-        <v>0</v>
       </c>
       <c r="R22" s="9">
         <v>0</v>
       </c>
       <c r="S22" s="9">
+        <v>0</v>
+      </c>
+      <c r="T22" s="9">
         <v>1283</v>
       </c>
-      <c r="T22" s="10">
+      <c r="U22" s="10">
         <v>-0.02</v>
       </c>
-      <c r="U22" s="9">
+      <c r="V22" s="9">
         <v>53</v>
       </c>
-      <c r="V22" s="10">
+      <c r="W22" s="10">
         <v>0.23</v>
       </c>
-      <c r="W22" s="9">
+      <c r="X22" s="9">
         <v>70</v>
       </c>
-      <c r="X22" s="9">
+      <c r="Y22" s="9">
         <v>106</v>
       </c>
-      <c r="Y22" s="9">
+      <c r="Z22" s="9">
         <v>105</v>
       </c>
-      <c r="Z22" s="9">
+      <c r="AA22" s="9">
         <v>106</v>
       </c>
-      <c r="AA22" s="9">
+      <c r="AB22" s="9">
         <v>291</v>
       </c>
-      <c r="AB22" s="9">
+      <c r="AC22" s="9">
         <v>103</v>
       </c>
-      <c r="AC22" s="9">
+      <c r="AD22" s="9">
         <v>98</v>
       </c>
-      <c r="AD22" s="9">
+      <c r="AE22" s="9">
         <v>109</v>
       </c>
-      <c r="AE22" s="9"/>
-      <c r="AF22" s="9">
+      <c r="AF22" s="9"/>
+      <c r="AG22" s="9">
         <v>13</v>
       </c>
-      <c r="AG22" s="9">
+      <c r="AH22" s="9">
         <v>460</v>
       </c>
-      <c r="AH22" s="9">
+      <c r="AI22" s="9">
         <v>394</v>
       </c>
-      <c r="AI22" s="9">
+      <c r="AJ22" s="9">
         <v>107</v>
       </c>
-      <c r="AJ22" s="9">
+      <c r="AK22" s="9">
         <v>6</v>
       </c>
-      <c r="AK22" s="9">
+      <c r="AL22" s="9">
         <v>104</v>
       </c>
-      <c r="AL22" s="9">
+      <c r="AM22" s="9">
         <v>108</v>
       </c>
-      <c r="AM22" s="9">
+      <c r="AN22" s="9">
         <v>101</v>
       </c>
-      <c r="AN22" s="9">
+      <c r="AO22" s="9">
         <v>102</v>
       </c>
-      <c r="AO22" s="9">
+      <c r="AP22" s="9">
         <v>104</v>
       </c>
-      <c r="AP22" s="9">
+      <c r="AQ22" s="9">
         <v>98</v>
       </c>
-      <c r="AQ22" s="9">
+      <c r="AR22" s="9">
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>479</v>
       </c>
@@ -4989,102 +5159,105 @@
       <c r="K23" s="12" t="s">
         <v>489</v>
       </c>
-      <c r="L23" s="2">
+      <c r="L23" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="M23" s="2">
         <v>44796</v>
       </c>
-      <c r="M23" s="8" t="s">
+      <c r="N23" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="O23" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="P23" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="P23" s="9">
+      <c r="Q23" s="9">
         <v>77</v>
-      </c>
-      <c r="Q23" s="9">
-        <v>0</v>
       </c>
       <c r="R23" s="9">
         <v>0</v>
       </c>
       <c r="S23" s="9">
+        <v>0</v>
+      </c>
+      <c r="T23" s="9">
         <v>1552</v>
       </c>
-      <c r="T23" s="10">
+      <c r="U23" s="10">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="U23" s="9">
+      <c r="V23" s="9">
         <v>51</v>
       </c>
-      <c r="V23" s="10">
+      <c r="W23" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="W23" s="9">
+      <c r="X23" s="9">
         <v>62</v>
       </c>
-      <c r="X23" s="9">
+      <c r="Y23" s="9">
         <v>106</v>
       </c>
-      <c r="Y23" s="9">
+      <c r="Z23" s="9">
         <v>104</v>
       </c>
-      <c r="Z23" s="9">
+      <c r="AA23" s="9">
         <v>106</v>
       </c>
-      <c r="AA23" s="9">
+      <c r="AB23" s="9">
         <v>226</v>
       </c>
-      <c r="AB23" s="9">
+      <c r="AC23" s="9">
         <v>103</v>
       </c>
-      <c r="AC23" s="9">
+      <c r="AD23" s="9">
         <v>101</v>
       </c>
-      <c r="AD23" s="9">
+      <c r="AE23" s="9">
         <v>104</v>
       </c>
-      <c r="AE23" s="9"/>
-      <c r="AF23" s="9">
+      <c r="AF23" s="9"/>
+      <c r="AG23" s="9">
         <v>12</v>
       </c>
-      <c r="AG23" s="9">
+      <c r="AH23" s="9">
         <v>420</v>
       </c>
-      <c r="AH23" s="9">
+      <c r="AI23" s="9">
         <v>311</v>
       </c>
-      <c r="AI23" s="9">
+      <c r="AJ23" s="9">
         <v>107</v>
       </c>
-      <c r="AJ23" s="9">
+      <c r="AK23" s="9">
         <v>3</v>
       </c>
-      <c r="AK23" s="9">
+      <c r="AL23" s="9">
         <v>101</v>
       </c>
-      <c r="AL23" s="9">
+      <c r="AM23" s="9">
         <v>108</v>
       </c>
-      <c r="AM23" s="9">
+      <c r="AN23" s="9">
         <v>103</v>
       </c>
-      <c r="AN23" s="9">
+      <c r="AO23" s="9">
         <v>101</v>
       </c>
-      <c r="AO23" s="9">
+      <c r="AP23" s="9">
         <v>100</v>
       </c>
-      <c r="AP23" s="9">
+      <c r="AQ23" s="9">
         <v>104</v>
       </c>
-      <c r="AQ23" s="9">
+      <c r="AR23" s="9">
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13" t="s">
         <v>490</v>
       </c>
@@ -5118,104 +5291,107 @@
       <c r="K24" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="L24" s="2">
+      <c r="L24" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="M24" s="2">
         <v>44586</v>
       </c>
-      <c r="M24" s="8" t="s">
+      <c r="N24" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="O24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="P24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P24" s="9">
+      <c r="Q24" s="9">
         <v>80</v>
-      </c>
-      <c r="Q24" s="9">
-        <v>0</v>
       </c>
       <c r="R24" s="9">
         <v>0</v>
       </c>
       <c r="S24" s="9">
+        <v>0</v>
+      </c>
+      <c r="T24" s="9">
         <v>1684</v>
       </c>
-      <c r="T24" s="10">
+      <c r="U24" s="10">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="U24" s="9">
+      <c r="V24" s="9">
         <v>65</v>
       </c>
-      <c r="V24" s="10">
+      <c r="W24" s="10">
         <v>0.03</v>
       </c>
-      <c r="W24" s="9">
+      <c r="X24" s="9">
         <v>63</v>
       </c>
-      <c r="X24" s="9">
+      <c r="Y24" s="9">
         <v>100</v>
       </c>
-      <c r="Y24" s="9">
+      <c r="Z24" s="9">
         <v>108</v>
       </c>
-      <c r="Z24" s="9">
+      <c r="AA24" s="9">
         <v>104</v>
       </c>
-      <c r="AA24" s="9">
+      <c r="AB24" s="9">
         <v>250</v>
       </c>
-      <c r="AB24" s="9">
+      <c r="AC24" s="9">
         <v>104</v>
       </c>
-      <c r="AC24" s="9">
+      <c r="AD24" s="9">
         <v>98</v>
-      </c>
-      <c r="AD24" s="9">
-        <v>100</v>
       </c>
       <c r="AE24" s="9">
         <v>100</v>
       </c>
       <c r="AF24" s="9">
+        <v>100</v>
+      </c>
+      <c r="AG24" s="9">
         <v>14</v>
       </c>
-      <c r="AG24" s="9">
+      <c r="AH24" s="9">
         <v>466</v>
       </c>
-      <c r="AH24" s="9">
+      <c r="AI24" s="9">
         <v>219</v>
       </c>
-      <c r="AI24" s="9">
+      <c r="AJ24" s="9">
         <v>109</v>
       </c>
-      <c r="AJ24" s="9">
+      <c r="AK24" s="9">
         <v>3</v>
       </c>
-      <c r="AK24" s="9">
+      <c r="AL24" s="9">
         <v>102</v>
       </c>
-      <c r="AL24" s="9">
+      <c r="AM24" s="9">
         <v>106</v>
       </c>
-      <c r="AM24" s="9">
+      <c r="AN24" s="9">
         <v>94</v>
       </c>
-      <c r="AN24" s="9">
+      <c r="AO24" s="9">
         <v>103</v>
       </c>
-      <c r="AO24" s="9">
+      <c r="AP24" s="9">
         <v>102</v>
       </c>
-      <c r="AP24" s="9">
+      <c r="AQ24" s="9">
         <v>106</v>
       </c>
-      <c r="AQ24" s="9">
+      <c r="AR24" s="9">
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>498</v>
       </c>
@@ -5249,102 +5425,105 @@
       <c r="K25" s="12" t="s">
         <v>508</v>
       </c>
-      <c r="L25" s="2">
+      <c r="L25" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="M25" s="2">
         <v>45105</v>
       </c>
-      <c r="M25" s="8" t="s">
+      <c r="N25" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="O25" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O25" s="2" t="s">
+      <c r="P25" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="P25" s="9">
+      <c r="Q25" s="9">
         <v>78</v>
-      </c>
-      <c r="Q25" s="9">
-        <v>0</v>
       </c>
       <c r="R25" s="9">
         <v>0</v>
       </c>
       <c r="S25" s="9">
+        <v>0</v>
+      </c>
+      <c r="T25" s="9">
         <v>1290</v>
       </c>
-      <c r="T25" s="10">
+      <c r="U25" s="10">
         <v>0.06</v>
       </c>
-      <c r="U25" s="9">
+      <c r="V25" s="9">
         <v>62</v>
       </c>
-      <c r="V25" s="10">
+      <c r="W25" s="10">
         <v>0.11</v>
       </c>
-      <c r="W25" s="9">
+      <c r="X25" s="9">
         <v>57</v>
       </c>
-      <c r="X25" s="9">
+      <c r="Y25" s="9">
         <v>109</v>
       </c>
-      <c r="Y25" s="9">
+      <c r="Z25" s="9">
         <v>103</v>
       </c>
-      <c r="Z25" s="9">
+      <c r="AA25" s="9">
         <v>107</v>
       </c>
-      <c r="AA25" s="9">
+      <c r="AB25" s="9">
         <v>293</v>
       </c>
-      <c r="AB25" s="9">
+      <c r="AC25" s="9">
         <v>106</v>
       </c>
-      <c r="AC25" s="9">
+      <c r="AD25" s="9">
         <v>99</v>
       </c>
-      <c r="AD25" s="9">
+      <c r="AE25" s="9">
         <v>103</v>
       </c>
-      <c r="AE25" s="9"/>
-      <c r="AF25" s="9">
+      <c r="AF25" s="9"/>
+      <c r="AG25" s="9">
         <v>12</v>
       </c>
-      <c r="AG25" s="9">
+      <c r="AH25" s="9">
         <v>431</v>
       </c>
-      <c r="AH25" s="9">
+      <c r="AI25" s="9">
         <v>660</v>
       </c>
-      <c r="AI25" s="9">
+      <c r="AJ25" s="9">
         <v>105</v>
       </c>
-      <c r="AJ25" s="9">
+      <c r="AK25" s="9">
         <v>7</v>
       </c>
-      <c r="AK25" s="9">
+      <c r="AL25" s="9">
         <v>107</v>
       </c>
-      <c r="AL25" s="9">
+      <c r="AM25" s="9">
         <v>112</v>
       </c>
-      <c r="AM25" s="9">
+      <c r="AN25" s="9">
         <v>104</v>
       </c>
-      <c r="AN25" s="9">
+      <c r="AO25" s="9">
         <v>101</v>
       </c>
-      <c r="AO25" s="9">
+      <c r="AP25" s="9">
         <v>99</v>
       </c>
-      <c r="AP25" s="9">
+      <c r="AQ25" s="9">
         <v>102</v>
       </c>
-      <c r="AQ25" s="9">
+      <c r="AR25" s="9">
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>509</v>
       </c>
@@ -5378,104 +5557,107 @@
       <c r="K26" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="L26" s="2">
+      <c r="L26" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="M26" s="2">
         <v>43921</v>
       </c>
-      <c r="M26" s="8" t="s">
+      <c r="N26" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="O26" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O26" s="2" t="s">
+      <c r="P26" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P26" s="9">
+      <c r="Q26" s="9">
         <v>82</v>
       </c>
-      <c r="Q26" s="9">
+      <c r="R26" s="9">
         <v>435</v>
       </c>
-      <c r="R26" s="9">
+      <c r="S26" s="9">
         <v>109</v>
       </c>
-      <c r="S26" s="9">
+      <c r="T26" s="9">
         <v>1417</v>
       </c>
-      <c r="T26" s="10">
+      <c r="U26" s="10">
         <v>0.28000000000000003</v>
       </c>
-      <c r="U26" s="9">
+      <c r="V26" s="9">
         <v>92</v>
       </c>
-      <c r="V26" s="10">
+      <c r="W26" s="10">
         <v>0</v>
       </c>
-      <c r="W26" s="9">
+      <c r="X26" s="9">
         <v>50</v>
       </c>
-      <c r="X26" s="9">
+      <c r="Y26" s="9">
         <v>97</v>
       </c>
-      <c r="Y26" s="9">
+      <c r="Z26" s="9">
         <v>103</v>
       </c>
-      <c r="Z26" s="9">
+      <c r="AA26" s="9">
         <v>100</v>
       </c>
-      <c r="AA26" s="9">
+      <c r="AB26" s="9">
         <v>209</v>
       </c>
-      <c r="AB26" s="9">
+      <c r="AC26" s="9">
         <v>105</v>
       </c>
-      <c r="AC26" s="9">
+      <c r="AD26" s="9">
         <v>100</v>
       </c>
-      <c r="AD26" s="9">
+      <c r="AE26" s="9">
         <v>101</v>
       </c>
-      <c r="AE26" s="9">
+      <c r="AF26" s="9">
         <v>115</v>
       </c>
-      <c r="AF26" s="9">
+      <c r="AG26" s="9">
         <v>15</v>
       </c>
-      <c r="AG26" s="9">
+      <c r="AH26" s="9">
         <v>491</v>
       </c>
-      <c r="AH26" s="9">
+      <c r="AI26" s="9">
         <v>250</v>
       </c>
-      <c r="AI26" s="9">
+      <c r="AJ26" s="9">
         <v>110</v>
       </c>
-      <c r="AJ26" s="9">
+      <c r="AK26" s="9">
         <v>2</v>
       </c>
-      <c r="AK26" s="9">
+      <c r="AL26" s="9">
         <v>101</v>
       </c>
-      <c r="AL26" s="9">
+      <c r="AM26" s="9">
         <v>99</v>
       </c>
-      <c r="AM26" s="9">
+      <c r="AN26" s="9">
         <v>100</v>
       </c>
-      <c r="AN26" s="9">
+      <c r="AO26" s="9">
         <v>102</v>
       </c>
-      <c r="AO26" s="9">
+      <c r="AP26" s="9">
         <v>100</v>
       </c>
-      <c r="AP26" s="9">
+      <c r="AQ26" s="9">
         <v>103</v>
       </c>
-      <c r="AQ26" s="9">
+      <c r="AR26" s="9">
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="13" t="s">
         <v>517</v>
       </c>
@@ -5509,102 +5691,105 @@
       <c r="K27" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="L27" s="2">
+      <c r="L27" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="M27" s="2">
         <v>44682</v>
       </c>
-      <c r="M27" s="8" t="s">
+      <c r="N27" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="O27" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O27" s="2" t="s">
+      <c r="P27" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P27" s="9">
+      <c r="Q27" s="9">
         <v>81</v>
-      </c>
-      <c r="Q27" s="9">
-        <v>0</v>
       </c>
       <c r="R27" s="9">
         <v>0</v>
       </c>
       <c r="S27" s="9">
+        <v>0</v>
+      </c>
+      <c r="T27" s="9">
         <v>598</v>
       </c>
-      <c r="T27" s="10">
+      <c r="U27" s="10">
         <v>0.2</v>
       </c>
-      <c r="U27" s="9">
+      <c r="V27" s="9">
         <v>46</v>
       </c>
-      <c r="V27" s="10">
+      <c r="W27" s="10">
         <v>0.25</v>
       </c>
-      <c r="W27" s="9">
+      <c r="X27" s="9">
         <v>47</v>
       </c>
-      <c r="X27" s="9">
+      <c r="Y27" s="9">
         <v>106</v>
       </c>
-      <c r="Y27" s="9">
+      <c r="Z27" s="9">
         <v>104</v>
       </c>
-      <c r="Z27" s="9">
+      <c r="AA27" s="9">
         <v>106</v>
       </c>
-      <c r="AA27" s="9">
+      <c r="AB27" s="9">
         <v>227</v>
       </c>
-      <c r="AB27" s="9">
+      <c r="AC27" s="9">
         <v>100</v>
       </c>
-      <c r="AC27" s="9">
+      <c r="AD27" s="9">
         <v>106</v>
       </c>
-      <c r="AD27" s="9">
+      <c r="AE27" s="9">
         <v>110</v>
       </c>
-      <c r="AE27" s="9"/>
-      <c r="AF27" s="9">
+      <c r="AF27" s="9"/>
+      <c r="AG27" s="9">
         <v>11</v>
       </c>
-      <c r="AG27" s="9">
+      <c r="AH27" s="9">
         <v>340</v>
       </c>
-      <c r="AH27" s="9">
+      <c r="AI27" s="9">
         <v>346</v>
       </c>
-      <c r="AI27" s="9">
+      <c r="AJ27" s="9">
         <v>106</v>
       </c>
-      <c r="AJ27" s="9">
+      <c r="AK27" s="9">
         <v>4</v>
       </c>
-      <c r="AK27" s="9">
+      <c r="AL27" s="9">
         <v>98</v>
       </c>
-      <c r="AL27" s="9">
+      <c r="AM27" s="9">
         <v>110</v>
       </c>
-      <c r="AM27" s="9">
+      <c r="AN27" s="9">
         <v>102</v>
       </c>
-      <c r="AN27" s="9">
+      <c r="AO27" s="9">
         <v>101</v>
       </c>
-      <c r="AO27" s="9">
+      <c r="AP27" s="9">
         <v>105</v>
       </c>
-      <c r="AP27" s="9">
+      <c r="AQ27" s="9">
         <v>103</v>
       </c>
-      <c r="AQ27" s="9">
+      <c r="AR27" s="9">
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:43" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>523</v>
       </c>
@@ -5638,102 +5823,105 @@
       <c r="K28" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="L28" s="2">
+      <c r="L28" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="M28" s="2">
         <v>44070</v>
       </c>
-      <c r="M28" s="8" t="s">
+      <c r="N28" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="N28" s="2" t="s">
+      <c r="O28" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O28" s="2" t="s">
+      <c r="P28" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P28" s="9">
+      <c r="Q28" s="9">
         <v>92</v>
       </c>
-      <c r="Q28" s="9">
+      <c r="R28" s="9">
         <v>693</v>
       </c>
-      <c r="R28" s="9">
+      <c r="S28" s="9">
         <v>326</v>
       </c>
-      <c r="S28" s="9">
+      <c r="T28" s="9">
         <v>671</v>
       </c>
-      <c r="T28" s="10">
+      <c r="U28" s="10">
         <v>-0.17</v>
       </c>
-      <c r="U28" s="9">
+      <c r="V28" s="9">
         <v>11</v>
       </c>
-      <c r="V28" s="10">
+      <c r="W28" s="10">
         <v>0.12</v>
       </c>
-      <c r="W28" s="9">
+      <c r="X28" s="9">
         <v>36</v>
       </c>
-      <c r="X28" s="9">
+      <c r="Y28" s="9">
         <v>107</v>
       </c>
-      <c r="Y28" s="9">
+      <c r="Z28" s="9">
         <v>101</v>
       </c>
-      <c r="Z28" s="9">
+      <c r="AA28" s="9">
         <v>106</v>
       </c>
-      <c r="AA28" s="9">
+      <c r="AB28" s="9">
         <v>76</v>
       </c>
-      <c r="AB28" s="9">
+      <c r="AC28" s="9">
         <v>97</v>
       </c>
-      <c r="AC28" s="9">
+      <c r="AD28" s="9">
         <v>106</v>
       </c>
-      <c r="AD28" s="9">
+      <c r="AE28" s="9">
         <v>105</v>
       </c>
-      <c r="AE28" s="9"/>
-      <c r="AF28" s="9">
+      <c r="AF28" s="9"/>
+      <c r="AG28" s="9">
         <v>-1</v>
       </c>
-      <c r="AG28" s="9">
+      <c r="AH28" s="9">
         <v>188</v>
       </c>
-      <c r="AH28" s="9">
+      <c r="AI28" s="9">
         <v>254</v>
       </c>
-      <c r="AI28" s="9">
+      <c r="AJ28" s="9">
         <v>96</v>
       </c>
-      <c r="AJ28" s="9">
+      <c r="AK28" s="9">
         <v>2</v>
       </c>
-      <c r="AK28" s="9">
+      <c r="AL28" s="9">
         <v>96</v>
       </c>
-      <c r="AL28" s="9">
+      <c r="AM28" s="9">
         <v>106</v>
       </c>
-      <c r="AM28" s="9">
+      <c r="AN28" s="9">
         <v>103</v>
       </c>
-      <c r="AN28" s="9">
+      <c r="AO28" s="9">
         <v>107</v>
       </c>
-      <c r="AO28" s="9">
+      <c r="AP28" s="9">
         <v>101</v>
-      </c>
-      <c r="AP28" s="9">
-        <v>100</v>
       </c>
       <c r="AQ28" s="9">
         <v>100</v>
       </c>
+      <c r="AR28" s="9">
+        <v>100</v>
+      </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>52</v>
       </c>
@@ -5767,104 +5955,107 @@
       <c r="K29" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="L29" s="2">
+      <c r="L29" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="M29" s="2">
         <v>44430</v>
       </c>
-      <c r="M29" s="4" t="s">
+      <c r="N29" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N29" s="2" t="s">
+      <c r="O29" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O29" s="2" t="s">
+      <c r="P29" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P29" s="9">
+      <c r="Q29" s="9">
         <v>82</v>
-      </c>
-      <c r="Q29" s="9">
-        <v>0</v>
       </c>
       <c r="R29" s="9">
         <v>0</v>
       </c>
       <c r="S29" s="9">
+        <v>0</v>
+      </c>
+      <c r="T29" s="9">
         <v>1176</v>
       </c>
-      <c r="T29" s="10">
+      <c r="U29" s="10">
         <v>0.2</v>
       </c>
-      <c r="U29" s="9">
+      <c r="V29" s="9">
         <v>73</v>
       </c>
-      <c r="V29" s="10">
+      <c r="W29" s="10">
         <v>-0.03</v>
       </c>
-      <c r="W29" s="9">
+      <c r="X29" s="9">
         <v>40</v>
       </c>
-      <c r="X29" s="9">
+      <c r="Y29" s="9">
         <v>106</v>
-      </c>
-      <c r="Y29" s="9">
-        <v>107</v>
       </c>
       <c r="Z29" s="9">
         <v>107</v>
       </c>
       <c r="AA29" s="9">
+        <v>107</v>
+      </c>
+      <c r="AB29" s="9">
         <v>328</v>
       </c>
-      <c r="AB29" s="9">
+      <c r="AC29" s="9">
         <v>112</v>
       </c>
-      <c r="AC29" s="9">
+      <c r="AD29" s="9">
         <v>96</v>
       </c>
-      <c r="AD29" s="9">
+      <c r="AE29" s="9">
         <v>105</v>
       </c>
-      <c r="AE29" s="9">
+      <c r="AF29" s="9">
         <v>100</v>
       </c>
-      <c r="AF29" s="9">
+      <c r="AG29" s="9">
         <v>16</v>
       </c>
-      <c r="AG29" s="9">
+      <c r="AH29" s="9">
         <v>391</v>
       </c>
-      <c r="AH29" s="9">
+      <c r="AI29" s="9">
         <v>915</v>
       </c>
-      <c r="AI29" s="9">
+      <c r="AJ29" s="9">
         <v>106</v>
       </c>
-      <c r="AJ29" s="9">
+      <c r="AK29" s="9">
         <v>6</v>
       </c>
-      <c r="AK29" s="9">
+      <c r="AL29" s="9">
         <v>112</v>
       </c>
-      <c r="AL29" s="9">
+      <c r="AM29" s="9">
         <v>102</v>
       </c>
-      <c r="AM29" s="9">
+      <c r="AN29" s="9">
         <v>105</v>
       </c>
-      <c r="AN29" s="9">
+      <c r="AO29" s="9">
         <v>101</v>
       </c>
-      <c r="AO29" s="9">
+      <c r="AP29" s="9">
         <v>103</v>
       </c>
-      <c r="AP29" s="9">
+      <c r="AQ29" s="9">
         <v>101</v>
       </c>
-      <c r="AQ29" s="9">
+      <c r="AR29" s="9">
         <v>99</v>
       </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>41</v>
       </c>
@@ -5898,102 +6089,105 @@
       <c r="K30" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="L30" s="2">
+      <c r="L30" s="16" t="s">
+        <v>552</v>
+      </c>
+      <c r="M30" s="2">
         <v>44852</v>
       </c>
-      <c r="M30" s="4" t="s">
+      <c r="N30" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="O30" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O30" s="2" t="s">
+      <c r="P30" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P30" s="9">
+      <c r="Q30" s="9">
         <v>79</v>
-      </c>
-      <c r="Q30" s="9">
-        <v>0</v>
       </c>
       <c r="R30" s="9">
         <v>0</v>
       </c>
       <c r="S30" s="9">
+        <v>0</v>
+      </c>
+      <c r="T30" s="9">
         <v>697</v>
       </c>
-      <c r="T30" s="10">
+      <c r="U30" s="10">
         <v>0.39</v>
       </c>
-      <c r="U30" s="9">
+      <c r="V30" s="9">
         <v>68</v>
       </c>
-      <c r="V30" s="10">
+      <c r="W30" s="10">
         <v>0.21</v>
       </c>
-      <c r="W30" s="9">
+      <c r="X30" s="9">
         <v>45</v>
-      </c>
-      <c r="X30" s="9">
-        <v>103</v>
       </c>
       <c r="Y30" s="9">
         <v>103</v>
       </c>
       <c r="Z30" s="9">
+        <v>103</v>
+      </c>
+      <c r="AA30" s="9">
         <v>105</v>
       </c>
-      <c r="AA30" s="9">
+      <c r="AB30" s="9">
         <v>203</v>
       </c>
-      <c r="AB30" s="9">
+      <c r="AC30" s="9">
         <v>100</v>
       </c>
-      <c r="AC30" s="9">
+      <c r="AD30" s="9">
         <v>103</v>
       </c>
-      <c r="AD30" s="9">
+      <c r="AE30" s="9">
         <v>110</v>
       </c>
-      <c r="AE30" s="9"/>
-      <c r="AF30" s="9">
+      <c r="AF30" s="9"/>
+      <c r="AG30" s="9">
         <v>8</v>
       </c>
-      <c r="AG30" s="9">
+      <c r="AH30" s="9">
         <v>398</v>
       </c>
-      <c r="AH30" s="9">
+      <c r="AI30" s="9">
         <v>665</v>
       </c>
-      <c r="AI30" s="9">
+      <c r="AJ30" s="9">
         <v>101</v>
       </c>
-      <c r="AJ30" s="9">
+      <c r="AK30" s="9">
         <v>4</v>
-      </c>
-      <c r="AK30" s="9">
-        <v>101</v>
       </c>
       <c r="AL30" s="9">
         <v>101</v>
       </c>
       <c r="AM30" s="9">
+        <v>101</v>
+      </c>
+      <c r="AN30" s="9">
         <v>105</v>
       </c>
-      <c r="AN30" s="9">
+      <c r="AO30" s="9">
         <v>98</v>
-      </c>
-      <c r="AO30" s="9">
-        <v>101</v>
       </c>
       <c r="AP30" s="9">
         <v>101</v>
       </c>
       <c r="AQ30" s="9">
+        <v>101</v>
+      </c>
+      <c r="AR30" s="9">
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>63</v>
       </c>
@@ -6027,102 +6221,105 @@
       <c r="K31" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="L31" s="2">
+      <c r="L31" s="16" t="s">
+        <v>553</v>
+      </c>
+      <c r="M31" s="2">
         <v>43400</v>
       </c>
-      <c r="M31" s="4" t="s">
+      <c r="N31" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="O31" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="O31" s="2" t="s">
+      <c r="P31" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="P31" s="9">
+      <c r="Q31" s="9">
         <v>98</v>
       </c>
-      <c r="Q31" s="9">
+      <c r="R31" s="9">
         <v>1280</v>
       </c>
-      <c r="R31" s="9">
+      <c r="S31" s="9">
         <v>498</v>
       </c>
-      <c r="S31" s="9">
+      <c r="T31" s="9">
         <v>532</v>
       </c>
-      <c r="T31" s="10">
+      <c r="U31" s="10">
         <v>0.25</v>
       </c>
-      <c r="U31" s="9">
+      <c r="V31" s="9">
         <v>47</v>
       </c>
-      <c r="V31" s="10">
+      <c r="W31" s="10">
         <v>0.1</v>
       </c>
-      <c r="W31" s="9">
+      <c r="X31" s="9">
         <v>29</v>
       </c>
-      <c r="X31" s="9">
+      <c r="Y31" s="9">
         <v>99</v>
       </c>
-      <c r="Y31" s="9">
+      <c r="Z31" s="9">
         <v>104</v>
       </c>
-      <c r="Z31" s="9">
+      <c r="AA31" s="9">
         <v>102</v>
       </c>
-      <c r="AA31" s="9">
+      <c r="AB31" s="9">
         <v>93</v>
       </c>
-      <c r="AB31" s="9">
+      <c r="AC31" s="9">
         <v>102</v>
       </c>
-      <c r="AC31" s="9">
+      <c r="AD31" s="9">
         <v>99</v>
       </c>
-      <c r="AD31" s="9">
+      <c r="AE31" s="9">
         <v>107</v>
       </c>
-      <c r="AE31" s="9"/>
-      <c r="AF31" s="9">
+      <c r="AF31" s="9"/>
+      <c r="AG31" s="9">
         <v>5</v>
       </c>
-      <c r="AG31" s="9">
+      <c r="AH31" s="9">
         <v>266</v>
       </c>
-      <c r="AH31" s="9">
+      <c r="AI31" s="9">
         <v>364</v>
       </c>
-      <c r="AI31" s="9">
+      <c r="AJ31" s="9">
         <v>100</v>
       </c>
-      <c r="AJ31" s="9">
+      <c r="AK31" s="9">
         <v>2</v>
       </c>
-      <c r="AK31" s="9">
+      <c r="AL31" s="9">
         <v>99</v>
       </c>
-      <c r="AL31" s="9">
+      <c r="AM31" s="9">
         <v>102</v>
-      </c>
-      <c r="AM31" s="9">
-        <v>105</v>
       </c>
       <c r="AN31" s="9">
         <v>105</v>
       </c>
       <c r="AO31" s="9">
+        <v>105</v>
+      </c>
+      <c r="AP31" s="9">
         <v>98</v>
       </c>
-      <c r="AP31" s="9">
+      <c r="AQ31" s="9">
         <v>107</v>
       </c>
-      <c r="AQ31" s="9">
+      <c r="AR31" s="9">
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>74</v>
       </c>
@@ -6156,104 +6353,107 @@
       <c r="K32" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="L32" s="2">
+      <c r="L32" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M32" s="2">
         <v>44588</v>
       </c>
-      <c r="M32" s="4" t="s">
+      <c r="N32" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N32" s="2" t="s">
+      <c r="O32" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O32" s="2" t="s">
+      <c r="P32" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P32" s="9">
+      <c r="Q32" s="9">
         <v>80</v>
-      </c>
-      <c r="Q32" s="9">
-        <v>0</v>
       </c>
       <c r="R32" s="9">
         <v>0</v>
       </c>
       <c r="S32" s="9">
+        <v>0</v>
+      </c>
+      <c r="T32" s="9">
         <v>2059</v>
       </c>
-      <c r="T32" s="10">
+      <c r="U32" s="10">
         <v>-0.4</v>
       </c>
-      <c r="U32" s="9">
+      <c r="V32" s="9">
         <v>49</v>
       </c>
-      <c r="V32" s="10">
+      <c r="W32" s="10">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="W32" s="9">
+      <c r="X32" s="9">
         <v>67</v>
       </c>
-      <c r="X32" s="9">
+      <c r="Y32" s="9">
         <v>97</v>
       </c>
-      <c r="Y32" s="9">
+      <c r="Z32" s="9">
         <v>109</v>
       </c>
-      <c r="Z32" s="9">
+      <c r="AA32" s="9">
         <v>103</v>
       </c>
-      <c r="AA32" s="9">
+      <c r="AB32" s="9">
         <v>186</v>
       </c>
-      <c r="AB32" s="9">
+      <c r="AC32" s="9">
         <v>107</v>
       </c>
-      <c r="AC32" s="9">
+      <c r="AD32" s="9">
         <v>99</v>
       </c>
-      <c r="AD32" s="9">
+      <c r="AE32" s="9">
         <v>98</v>
       </c>
-      <c r="AE32" s="9">
+      <c r="AF32" s="9">
         <v>97</v>
       </c>
-      <c r="AF32" s="9">
+      <c r="AG32" s="9">
         <v>8</v>
       </c>
-      <c r="AG32" s="9">
+      <c r="AH32" s="9">
         <v>435</v>
       </c>
-      <c r="AH32" s="9">
+      <c r="AI32" s="9">
         <v>266</v>
       </c>
-      <c r="AI32" s="9">
+      <c r="AJ32" s="9">
         <v>103</v>
       </c>
-      <c r="AJ32" s="9">
+      <c r="AK32" s="9">
         <v>3</v>
       </c>
-      <c r="AK32" s="9">
+      <c r="AL32" s="9">
         <v>104</v>
       </c>
-      <c r="AL32" s="9">
+      <c r="AM32" s="9">
         <v>103</v>
       </c>
-      <c r="AM32" s="9">
+      <c r="AN32" s="9">
         <v>105</v>
       </c>
-      <c r="AN32" s="9">
+      <c r="AO32" s="9">
         <v>102</v>
       </c>
-      <c r="AO32" s="9">
+      <c r="AP32" s="9">
         <v>100</v>
       </c>
-      <c r="AP32" s="9">
+      <c r="AQ32" s="9">
         <v>102</v>
       </c>
-      <c r="AQ32" s="9">
+      <c r="AR32" s="9">
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>85</v>
       </c>
@@ -6287,102 +6487,105 @@
       <c r="K33" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="L33" s="2">
+      <c r="L33" s="16" t="s">
+        <v>554</v>
+      </c>
+      <c r="M33" s="2">
         <v>45111</v>
       </c>
-      <c r="M33" s="4" t="s">
+      <c r="N33" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N33" s="2" t="s">
+      <c r="O33" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O33" s="5" t="s">
+      <c r="P33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="P33" s="9">
+      <c r="Q33" s="9">
         <v>77</v>
-      </c>
-      <c r="Q33" s="9">
-        <v>0</v>
       </c>
       <c r="R33" s="9">
         <v>0</v>
       </c>
       <c r="S33" s="9">
+        <v>0</v>
+      </c>
+      <c r="T33" s="9">
         <v>1124</v>
       </c>
-      <c r="T33" s="10">
+      <c r="U33" s="10">
         <v>0.19</v>
       </c>
-      <c r="U33" s="9">
+      <c r="V33" s="9">
         <v>69</v>
       </c>
-      <c r="V33" s="10">
+      <c r="W33" s="10">
         <v>0.03</v>
       </c>
-      <c r="W33" s="9">
+      <c r="X33" s="9">
         <v>44</v>
       </c>
-      <c r="X33" s="9">
+      <c r="Y33" s="9">
         <v>104</v>
       </c>
-      <c r="Y33" s="9">
+      <c r="Z33" s="9">
         <v>114</v>
       </c>
-      <c r="Z33" s="9">
+      <c r="AA33" s="9">
         <v>110</v>
       </c>
-      <c r="AA33" s="9">
+      <c r="AB33" s="9">
         <v>270</v>
       </c>
-      <c r="AB33" s="9">
+      <c r="AC33" s="9">
         <v>106</v>
       </c>
-      <c r="AC33" s="9">
+      <c r="AD33" s="9">
         <v>98</v>
       </c>
-      <c r="AD33" s="9">
+      <c r="AE33" s="9">
         <v>103</v>
       </c>
-      <c r="AE33" s="9"/>
-      <c r="AF33" s="9">
+      <c r="AF33" s="9"/>
+      <c r="AG33" s="9">
         <v>13</v>
       </c>
-      <c r="AG33" s="9">
+      <c r="AH33" s="9">
         <v>396</v>
       </c>
-      <c r="AH33" s="9">
+      <c r="AI33" s="9">
         <v>566</v>
       </c>
-      <c r="AI33" s="9">
+      <c r="AJ33" s="9">
         <v>105</v>
       </c>
-      <c r="AJ33" s="9">
+      <c r="AK33" s="9">
         <v>4</v>
       </c>
-      <c r="AK33" s="9">
+      <c r="AL33" s="9">
         <v>106</v>
       </c>
-      <c r="AL33" s="9">
+      <c r="AM33" s="9">
         <v>104</v>
       </c>
-      <c r="AM33" s="9">
+      <c r="AN33" s="9">
         <v>102</v>
       </c>
-      <c r="AN33" s="9">
+      <c r="AO33" s="9">
         <v>104</v>
       </c>
-      <c r="AO33" s="9">
+      <c r="AP33" s="9">
         <v>101</v>
       </c>
-      <c r="AP33" s="9">
+      <c r="AQ33" s="9">
         <v>103</v>
       </c>
-      <c r="AQ33" s="9">
+      <c r="AR33" s="9">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>382</v>
       </c>
@@ -6416,102 +6619,105 @@
       <c r="K34" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="L34" s="2">
+      <c r="L34" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="M34" s="2">
         <v>45136</v>
       </c>
-      <c r="M34" s="4" t="s">
+      <c r="N34" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N34" s="2" t="s">
+      <c r="O34" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O34" s="2" t="s">
+      <c r="P34" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P34" s="9">
+      <c r="Q34" s="9">
         <v>78</v>
-      </c>
-      <c r="Q34" s="9">
-        <v>0</v>
       </c>
       <c r="R34" s="9">
         <v>0</v>
       </c>
       <c r="S34" s="9">
+        <v>0</v>
+      </c>
+      <c r="T34" s="9">
         <v>996</v>
       </c>
-      <c r="T34" s="10">
+      <c r="U34" s="10">
         <v>0.2</v>
       </c>
-      <c r="U34" s="9">
+      <c r="V34" s="9">
         <v>64</v>
       </c>
-      <c r="V34" s="10">
+      <c r="W34" s="10">
         <v>0.28000000000000003</v>
       </c>
-      <c r="W34" s="9">
+      <c r="X34" s="9">
         <v>63</v>
       </c>
-      <c r="X34" s="9">
+      <c r="Y34" s="9">
         <v>106</v>
       </c>
-      <c r="Y34" s="9">
+      <c r="Z34" s="9">
         <v>107</v>
       </c>
-      <c r="Z34" s="9">
+      <c r="AA34" s="9">
         <v>109</v>
       </c>
-      <c r="AA34" s="9">
+      <c r="AB34" s="9">
         <v>235</v>
       </c>
-      <c r="AB34" s="9">
+      <c r="AC34" s="9">
         <v>102</v>
       </c>
-      <c r="AC34" s="9">
+      <c r="AD34" s="9">
         <v>97</v>
       </c>
-      <c r="AD34" s="9">
+      <c r="AE34" s="9">
         <v>103</v>
       </c>
-      <c r="AE34" s="9"/>
-      <c r="AF34" s="9">
+      <c r="AF34" s="9"/>
+      <c r="AG34" s="9">
         <v>8</v>
       </c>
-      <c r="AG34" s="9">
+      <c r="AH34" s="9">
         <v>463</v>
       </c>
-      <c r="AH34" s="9">
+      <c r="AI34" s="9">
         <v>85</v>
       </c>
-      <c r="AI34" s="9">
+      <c r="AJ34" s="9">
         <v>105</v>
       </c>
-      <c r="AJ34" s="9">
+      <c r="AK34" s="9">
         <v>4</v>
       </c>
-      <c r="AK34" s="9">
+      <c r="AL34" s="9">
         <v>101</v>
       </c>
-      <c r="AL34" s="9">
+      <c r="AM34" s="9">
         <v>107</v>
       </c>
-      <c r="AM34" s="9">
+      <c r="AN34" s="9">
         <v>103</v>
       </c>
-      <c r="AN34" s="9">
+      <c r="AO34" s="9">
         <v>102</v>
       </c>
-      <c r="AO34" s="9">
+      <c r="AP34" s="9">
         <v>103</v>
       </c>
-      <c r="AP34" s="9">
+      <c r="AQ34" s="9">
         <v>101</v>
       </c>
-      <c r="AQ34" s="9">
+      <c r="AR34" s="9">
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>55</v>
       </c>
@@ -6545,104 +6751,107 @@
       <c r="K35" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="L35" s="2">
+      <c r="L35" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="M35" s="2">
         <v>43752</v>
       </c>
-      <c r="M35" s="4" t="s">
+      <c r="N35" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N35" s="2" t="s">
+      <c r="O35" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O35" s="5" t="s">
+      <c r="P35" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="P35" s="9">
+      <c r="Q35" s="9">
         <v>95</v>
       </c>
-      <c r="Q35" s="9">
+      <c r="R35" s="9">
         <v>6507</v>
       </c>
-      <c r="R35" s="9">
+      <c r="S35" s="9">
         <v>1665</v>
       </c>
-      <c r="S35" s="9">
+      <c r="T35" s="9">
         <v>1949</v>
       </c>
-      <c r="T35" s="10">
+      <c r="U35" s="10">
         <v>-0.25</v>
       </c>
-      <c r="U35" s="9">
+      <c r="V35" s="9">
         <v>60</v>
       </c>
-      <c r="V35" s="10">
+      <c r="W35" s="10">
         <v>-0.15</v>
       </c>
-      <c r="W35" s="9">
+      <c r="X35" s="9">
         <v>54</v>
       </c>
-      <c r="X35" s="9">
+      <c r="Y35" s="9">
         <v>99</v>
       </c>
-      <c r="Y35" s="9">
+      <c r="Z35" s="9">
         <v>109</v>
       </c>
-      <c r="Z35" s="9">
+      <c r="AA35" s="9">
         <v>102</v>
       </c>
-      <c r="AA35" s="9">
+      <c r="AB35" s="9">
         <v>245</v>
       </c>
-      <c r="AB35" s="9">
+      <c r="AC35" s="9">
         <v>108</v>
       </c>
-      <c r="AC35" s="9">
+      <c r="AD35" s="9">
         <v>101</v>
       </c>
-      <c r="AD35" s="9">
+      <c r="AE35" s="9">
         <v>98</v>
       </c>
-      <c r="AE35" s="9">
+      <c r="AF35" s="9">
         <v>88</v>
       </c>
-      <c r="AF35" s="9">
+      <c r="AG35" s="9">
         <v>13</v>
       </c>
-      <c r="AG35" s="9">
+      <c r="AH35" s="9">
         <v>412</v>
       </c>
-      <c r="AH35" s="9">
+      <c r="AI35" s="9">
         <v>416</v>
       </c>
-      <c r="AI35" s="9">
+      <c r="AJ35" s="9">
         <v>106</v>
       </c>
-      <c r="AJ35" s="9">
+      <c r="AK35" s="9">
         <v>5</v>
       </c>
-      <c r="AK35" s="9">
+      <c r="AL35" s="9">
         <v>105</v>
       </c>
-      <c r="AL35" s="9">
+      <c r="AM35" s="9">
         <v>102</v>
       </c>
-      <c r="AM35" s="9">
+      <c r="AN35" s="9">
         <v>104</v>
-      </c>
-      <c r="AN35" s="9">
-        <v>103</v>
       </c>
       <c r="AO35" s="9">
         <v>103</v>
       </c>
       <c r="AP35" s="9">
+        <v>103</v>
+      </c>
+      <c r="AQ35" s="9">
         <v>104</v>
       </c>
-      <c r="AQ35" s="9">
+      <c r="AR35" s="9">
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
         <v>374</v>
       </c>
@@ -6676,102 +6885,105 @@
       <c r="K36" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="L36" s="2">
+      <c r="L36" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="M36" s="2">
         <v>45289</v>
       </c>
-      <c r="M36" s="4" t="s">
+      <c r="N36" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N36" s="2" t="s">
+      <c r="O36" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O36" s="5" t="s">
+      <c r="P36" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="P36" s="9">
+      <c r="Q36" s="9">
         <v>76</v>
-      </c>
-      <c r="Q36" s="9">
-        <v>0</v>
       </c>
       <c r="R36" s="9">
         <v>0</v>
       </c>
       <c r="S36" s="9">
+        <v>0</v>
+      </c>
+      <c r="T36" s="9">
         <v>800</v>
       </c>
-      <c r="T36" s="10">
+      <c r="U36" s="10">
         <v>0.61</v>
       </c>
-      <c r="U36" s="9">
+      <c r="V36" s="9">
         <v>94</v>
       </c>
-      <c r="V36" s="10">
+      <c r="W36" s="10">
         <v>0.22</v>
       </c>
-      <c r="W36" s="9">
+      <c r="X36" s="9">
         <v>50</v>
       </c>
-      <c r="X36" s="9">
+      <c r="Y36" s="9">
         <v>110</v>
       </c>
-      <c r="Y36" s="9">
+      <c r="Z36" s="9">
         <v>103</v>
       </c>
-      <c r="Z36" s="9">
+      <c r="AA36" s="9">
         <v>110</v>
       </c>
-      <c r="AA36" s="9">
+      <c r="AB36" s="9">
         <v>304</v>
       </c>
-      <c r="AB36" s="9">
+      <c r="AC36" s="9">
         <v>108</v>
       </c>
-      <c r="AC36" s="9">
+      <c r="AD36" s="9">
         <v>99</v>
       </c>
-      <c r="AD36" s="9">
+      <c r="AE36" s="9">
         <v>109</v>
       </c>
-      <c r="AE36" s="9"/>
-      <c r="AF36" s="9">
+      <c r="AF36" s="9"/>
+      <c r="AG36" s="9">
         <v>10</v>
       </c>
-      <c r="AG36" s="9">
+      <c r="AH36" s="9">
         <v>497</v>
       </c>
-      <c r="AH36" s="9">
+      <c r="AI36" s="9">
         <v>638</v>
       </c>
-      <c r="AI36" s="9">
+      <c r="AJ36" s="9">
         <v>103</v>
       </c>
-      <c r="AJ36" s="9">
+      <c r="AK36" s="9">
         <v>6</v>
       </c>
-      <c r="AK36" s="9">
+      <c r="AL36" s="9">
         <v>106</v>
       </c>
-      <c r="AL36" s="9">
+      <c r="AM36" s="9">
         <v>110</v>
       </c>
-      <c r="AM36" s="9">
+      <c r="AN36" s="9">
         <v>108</v>
       </c>
-      <c r="AN36" s="9">
+      <c r="AO36" s="9">
         <v>99</v>
       </c>
-      <c r="AO36" s="9">
+      <c r="AP36" s="9">
         <v>101</v>
-      </c>
-      <c r="AP36" s="9">
-        <v>102</v>
       </c>
       <c r="AQ36" s="9">
         <v>102</v>
       </c>
+      <c r="AR36" s="9">
+        <v>102</v>
+      </c>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>366</v>
       </c>
@@ -6805,102 +7017,105 @@
       <c r="K37" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="L37" s="2">
+      <c r="L37" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="M37" s="2">
         <v>45202</v>
       </c>
-      <c r="M37" s="4" t="s">
+      <c r="N37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N37" s="2" t="s">
+      <c r="O37" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O37" s="5" t="s">
+      <c r="P37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="P37" s="9">
+      <c r="Q37" s="9">
         <v>77</v>
-      </c>
-      <c r="Q37" s="9">
-        <v>0</v>
       </c>
       <c r="R37" s="9">
         <v>0</v>
       </c>
       <c r="S37" s="9">
+        <v>0</v>
+      </c>
+      <c r="T37" s="9">
         <v>697</v>
       </c>
-      <c r="T37" s="10">
+      <c r="U37" s="10">
         <v>0.33</v>
       </c>
-      <c r="U37" s="9">
+      <c r="V37" s="9">
         <v>62</v>
       </c>
-      <c r="V37" s="10">
+      <c r="W37" s="10">
         <v>0.08</v>
       </c>
-      <c r="W37" s="9">
+      <c r="X37" s="9">
         <v>33</v>
-      </c>
-      <c r="X37" s="9">
-        <v>109</v>
       </c>
       <c r="Y37" s="9">
         <v>109</v>
       </c>
       <c r="Z37" s="9">
+        <v>109</v>
+      </c>
+      <c r="AA37" s="9">
         <v>111</v>
       </c>
-      <c r="AA37" s="9">
+      <c r="AB37" s="9">
         <v>248</v>
       </c>
-      <c r="AB37" s="9">
+      <c r="AC37" s="9">
         <v>103</v>
       </c>
-      <c r="AC37" s="9">
+      <c r="AD37" s="9">
         <v>101</v>
       </c>
-      <c r="AD37" s="9">
+      <c r="AE37" s="9">
         <v>109</v>
       </c>
-      <c r="AE37" s="9"/>
-      <c r="AF37" s="9">
+      <c r="AF37" s="9"/>
+      <c r="AG37" s="9">
         <v>9</v>
       </c>
-      <c r="AG37" s="9">
+      <c r="AH37" s="9">
         <v>328</v>
       </c>
-      <c r="AH37" s="9">
+      <c r="AI37" s="9">
         <v>606</v>
       </c>
-      <c r="AI37" s="9">
+      <c r="AJ37" s="9">
         <v>103</v>
       </c>
-      <c r="AJ37" s="9">
+      <c r="AK37" s="9">
         <v>5</v>
       </c>
-      <c r="AK37" s="9">
+      <c r="AL37" s="9">
         <v>103</v>
       </c>
-      <c r="AL37" s="9">
+      <c r="AM37" s="9">
         <v>113</v>
       </c>
-      <c r="AM37" s="9">
+      <c r="AN37" s="9">
         <v>105</v>
       </c>
-      <c r="AN37" s="9">
+      <c r="AO37" s="9">
         <v>97</v>
       </c>
-      <c r="AO37" s="9">
+      <c r="AP37" s="9">
         <v>100</v>
       </c>
-      <c r="AP37" s="9">
+      <c r="AQ37" s="9">
         <v>106</v>
       </c>
-      <c r="AQ37" s="9">
+      <c r="AR37" s="9">
         <v>102</v>
       </c>
     </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
         <v>358</v>
       </c>
@@ -6934,102 +7149,105 @@
       <c r="K38" s="12" t="s">
         <v>365</v>
       </c>
-      <c r="L38" s="2">
+      <c r="L38" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M38" s="2">
         <v>45483</v>
       </c>
-      <c r="M38" s="4" t="s">
+      <c r="N38" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N38" s="2" t="s">
+      <c r="O38" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O38" s="5" t="s">
+      <c r="P38" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="P38" s="9">
+      <c r="Q38" s="9">
         <v>76</v>
-      </c>
-      <c r="Q38" s="9">
-        <v>0</v>
       </c>
       <c r="R38" s="9">
         <v>0</v>
       </c>
       <c r="S38" s="9">
+        <v>0</v>
+      </c>
+      <c r="T38" s="9">
         <v>526</v>
       </c>
-      <c r="T38" s="10">
+      <c r="U38" s="10">
         <v>0.51</v>
       </c>
-      <c r="U38" s="9">
+      <c r="V38" s="9">
         <v>71</v>
       </c>
-      <c r="V38" s="10">
+      <c r="W38" s="10">
         <v>0.19</v>
       </c>
-      <c r="W38" s="9">
+      <c r="X38" s="9">
         <v>37</v>
       </c>
-      <c r="X38" s="9">
+      <c r="Y38" s="9">
         <v>113</v>
       </c>
-      <c r="Y38" s="9">
+      <c r="Z38" s="9">
         <v>107</v>
       </c>
-      <c r="Z38" s="9">
+      <c r="AA38" s="9">
         <v>111</v>
       </c>
-      <c r="AA38" s="9">
+      <c r="AB38" s="9">
         <v>337</v>
       </c>
-      <c r="AB38" s="9">
+      <c r="AC38" s="9">
         <v>105</v>
       </c>
-      <c r="AC38" s="9">
+      <c r="AD38" s="9">
         <v>104</v>
       </c>
-      <c r="AD38" s="9">
+      <c r="AE38" s="9">
         <v>105</v>
       </c>
-      <c r="AE38" s="9"/>
-      <c r="AF38" s="9">
+      <c r="AF38" s="9"/>
+      <c r="AG38" s="9">
         <v>13</v>
       </c>
-      <c r="AG38" s="9">
+      <c r="AH38" s="9">
         <v>372</v>
       </c>
-      <c r="AH38" s="9">
+      <c r="AI38" s="9">
         <v>674</v>
       </c>
-      <c r="AI38" s="9">
+      <c r="AJ38" s="9">
         <v>106</v>
       </c>
-      <c r="AJ38" s="9">
+      <c r="AK38" s="9">
         <v>7</v>
       </c>
-      <c r="AK38" s="9">
+      <c r="AL38" s="9">
         <v>105</v>
       </c>
-      <c r="AL38" s="9">
+      <c r="AM38" s="9">
         <v>110</v>
       </c>
-      <c r="AM38" s="9">
+      <c r="AN38" s="9">
         <v>105</v>
       </c>
-      <c r="AN38" s="9">
+      <c r="AO38" s="9">
         <v>103</v>
       </c>
-      <c r="AO38" s="9">
+      <c r="AP38" s="9">
         <v>107</v>
       </c>
-      <c r="AP38" s="9">
+      <c r="AQ38" s="9">
         <v>98</v>
       </c>
-      <c r="AQ38" s="9">
+      <c r="AR38" s="9">
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>350</v>
       </c>
@@ -7063,104 +7281,107 @@
       <c r="K39" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="L39" s="2">
+      <c r="L39" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="M39" s="2">
         <v>45199</v>
       </c>
-      <c r="M39" s="4" t="s">
+      <c r="N39" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N39" s="2" t="s">
+      <c r="O39" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O39" s="5" t="s">
+      <c r="P39" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="P39" s="9">
+      <c r="Q39" s="9">
         <v>78</v>
-      </c>
-      <c r="Q39" s="9">
-        <v>0</v>
       </c>
       <c r="R39" s="9">
         <v>0</v>
       </c>
       <c r="S39" s="9">
+        <v>0</v>
+      </c>
+      <c r="T39" s="9">
         <v>1980</v>
       </c>
-      <c r="T39" s="10">
+      <c r="U39" s="10">
         <v>-0.03</v>
       </c>
-      <c r="U39" s="9">
+      <c r="V39" s="9">
         <v>85</v>
       </c>
-      <c r="V39" s="10">
+      <c r="W39" s="10">
         <v>-0.1</v>
       </c>
-      <c r="W39" s="9">
+      <c r="X39" s="9">
         <v>61</v>
-      </c>
-      <c r="X39" s="9">
-        <v>106</v>
       </c>
       <c r="Y39" s="9">
         <v>106</v>
       </c>
       <c r="Z39" s="9">
+        <v>106</v>
+      </c>
+      <c r="AA39" s="9">
         <v>108</v>
       </c>
-      <c r="AA39" s="9">
+      <c r="AB39" s="9">
         <v>250</v>
       </c>
-      <c r="AB39" s="9">
+      <c r="AC39" s="9">
         <v>103</v>
       </c>
-      <c r="AC39" s="9">
+      <c r="AD39" s="9">
         <v>100</v>
       </c>
-      <c r="AD39" s="9">
+      <c r="AE39" s="9">
         <v>93</v>
       </c>
-      <c r="AE39" s="9">
+      <c r="AF39" s="9">
         <v>102</v>
       </c>
-      <c r="AF39" s="9">
+      <c r="AG39" s="9">
         <v>12</v>
       </c>
-      <c r="AG39" s="9">
+      <c r="AH39" s="9">
         <v>517</v>
       </c>
-      <c r="AH39" s="9">
+      <c r="AI39" s="9">
         <v>357</v>
       </c>
-      <c r="AI39" s="9">
+      <c r="AJ39" s="9">
         <v>106</v>
       </c>
-      <c r="AJ39" s="9">
+      <c r="AK39" s="9">
         <v>3</v>
       </c>
-      <c r="AK39" s="9">
+      <c r="AL39" s="9">
         <v>102</v>
       </c>
-      <c r="AL39" s="9">
+      <c r="AM39" s="9">
         <v>105</v>
       </c>
-      <c r="AM39" s="9">
+      <c r="AN39" s="9">
         <v>102</v>
       </c>
-      <c r="AN39" s="9">
+      <c r="AO39" s="9">
         <v>104</v>
       </c>
-      <c r="AO39" s="9">
+      <c r="AP39" s="9">
         <v>100</v>
       </c>
-      <c r="AP39" s="9">
+      <c r="AQ39" s="9">
         <v>108</v>
       </c>
-      <c r="AQ39" s="9">
+      <c r="AR39" s="9">
         <v>106</v>
       </c>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
         <v>342</v>
       </c>
@@ -7194,104 +7415,107 @@
       <c r="K40" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="L40" s="2">
+      <c r="L40" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="M40" s="2">
         <v>45129</v>
       </c>
-      <c r="M40" s="4" t="s">
+      <c r="N40" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N40" s="2" t="s">
+      <c r="O40" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O40" s="5" t="s">
+      <c r="P40" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="P40" s="9">
+      <c r="Q40" s="9">
         <v>78</v>
-      </c>
-      <c r="Q40" s="9">
-        <v>0</v>
       </c>
       <c r="R40" s="9">
         <v>0</v>
       </c>
       <c r="S40" s="9">
+        <v>0</v>
+      </c>
+      <c r="T40" s="9">
         <v>1928</v>
       </c>
-      <c r="T40" s="10">
+      <c r="U40" s="10">
         <v>-0.15</v>
       </c>
-      <c r="U40" s="9">
+      <c r="V40" s="9">
         <v>70</v>
       </c>
-      <c r="V40" s="10">
+      <c r="W40" s="10">
         <v>-0.03</v>
       </c>
-      <c r="W40" s="9">
+      <c r="X40" s="9">
         <v>67</v>
       </c>
-      <c r="X40" s="9">
+      <c r="Y40" s="9">
         <v>107</v>
       </c>
-      <c r="Y40" s="9">
+      <c r="Z40" s="9">
         <v>102</v>
       </c>
-      <c r="Z40" s="9">
+      <c r="AA40" s="9">
         <v>106</v>
       </c>
-      <c r="AA40" s="9">
+      <c r="AB40" s="9">
         <v>279</v>
       </c>
-      <c r="AB40" s="9">
+      <c r="AC40" s="9">
         <v>104</v>
       </c>
-      <c r="AC40" s="9">
+      <c r="AD40" s="9">
         <v>97</v>
       </c>
-      <c r="AD40" s="9">
+      <c r="AE40" s="9">
         <v>106</v>
       </c>
-      <c r="AE40" s="9">
+      <c r="AF40" s="9">
         <v>102</v>
       </c>
-      <c r="AF40" s="9">
+      <c r="AG40" s="9">
         <v>14</v>
       </c>
-      <c r="AG40" s="9">
+      <c r="AH40" s="9">
         <v>498</v>
       </c>
-      <c r="AH40" s="9">
+      <c r="AI40" s="9">
         <v>491</v>
       </c>
-      <c r="AI40" s="9">
+      <c r="AJ40" s="9">
         <v>108</v>
       </c>
-      <c r="AJ40" s="9">
+      <c r="AK40" s="9">
         <v>5</v>
       </c>
-      <c r="AK40" s="9">
+      <c r="AL40" s="9">
         <v>101</v>
       </c>
-      <c r="AL40" s="9">
+      <c r="AM40" s="9">
         <v>112</v>
       </c>
-      <c r="AM40" s="9">
+      <c r="AN40" s="9">
         <v>100</v>
       </c>
-      <c r="AN40" s="9">
+      <c r="AO40" s="9">
         <v>102</v>
       </c>
-      <c r="AO40" s="9">
+      <c r="AP40" s="9">
         <v>101</v>
       </c>
-      <c r="AP40" s="9">
+      <c r="AQ40" s="9">
         <v>106</v>
       </c>
-      <c r="AQ40" s="9">
+      <c r="AR40" s="9">
         <v>101</v>
       </c>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>334</v>
       </c>
@@ -7325,102 +7549,105 @@
       <c r="K41" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="L41" s="2">
+      <c r="L41" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="M41" s="2">
         <v>45247</v>
       </c>
-      <c r="M41" s="4" t="s">
+      <c r="N41" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N41" s="2" t="s">
+      <c r="O41" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O41" s="5" t="s">
+      <c r="P41" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="P41" s="9">
+      <c r="Q41" s="9">
         <v>74</v>
-      </c>
-      <c r="Q41" s="9">
-        <v>0</v>
       </c>
       <c r="R41" s="9">
         <v>0</v>
       </c>
       <c r="S41" s="9">
+        <v>0</v>
+      </c>
+      <c r="T41" s="9">
         <v>1474</v>
       </c>
-      <c r="T41" s="10">
+      <c r="U41" s="10">
         <v>-0.08</v>
       </c>
-      <c r="U41" s="9">
+      <c r="V41" s="9">
         <v>58</v>
       </c>
-      <c r="V41" s="10">
+      <c r="W41" s="10">
         <v>-0.05</v>
       </c>
-      <c r="W41" s="9">
+      <c r="X41" s="9">
         <v>48</v>
       </c>
-      <c r="X41" s="9">
+      <c r="Y41" s="9">
         <v>104</v>
       </c>
-      <c r="Y41" s="9">
+      <c r="Z41" s="9">
         <v>109</v>
       </c>
-      <c r="Z41" s="9">
+      <c r="AA41" s="9">
         <v>107</v>
       </c>
-      <c r="AA41" s="9">
+      <c r="AB41" s="9">
         <v>225</v>
       </c>
-      <c r="AB41" s="9">
+      <c r="AC41" s="9">
         <v>106</v>
       </c>
-      <c r="AC41" s="9">
+      <c r="AD41" s="9">
         <v>99</v>
       </c>
-      <c r="AD41" s="9">
+      <c r="AE41" s="9">
         <v>96</v>
       </c>
-      <c r="AE41" s="9"/>
-      <c r="AF41" s="9">
+      <c r="AF41" s="9"/>
+      <c r="AG41" s="9">
         <v>9</v>
       </c>
-      <c r="AG41" s="9">
+      <c r="AH41" s="9">
         <v>380</v>
       </c>
-      <c r="AH41" s="9">
+      <c r="AI41" s="9">
         <v>372</v>
       </c>
-      <c r="AI41" s="9">
+      <c r="AJ41" s="9">
         <v>104</v>
       </c>
-      <c r="AJ41" s="9">
+      <c r="AK41" s="9">
         <v>4</v>
       </c>
-      <c r="AK41" s="9">
+      <c r="AL41" s="9">
         <v>102</v>
       </c>
-      <c r="AL41" s="9">
+      <c r="AM41" s="9">
         <v>109</v>
-      </c>
-      <c r="AM41" s="9">
-        <v>101</v>
       </c>
       <c r="AN41" s="9">
         <v>101</v>
       </c>
       <c r="AO41" s="9">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AP41" s="9">
         <v>102</v>
       </c>
       <c r="AQ41" s="9">
+        <v>102</v>
+      </c>
+      <c r="AR41" s="9">
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
         <v>323</v>
       </c>
@@ -7454,102 +7681,105 @@
       <c r="K42" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="L42" s="2">
+      <c r="L42" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="M42" s="2">
         <v>45432</v>
       </c>
-      <c r="M42" s="4" t="s">
+      <c r="N42" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N42" s="2" t="s">
+      <c r="O42" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O42" s="5" t="s">
+      <c r="P42" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="P42" s="9">
+      <c r="Q42" s="9">
         <v>76</v>
-      </c>
-      <c r="Q42" s="9">
-        <v>0</v>
       </c>
       <c r="R42" s="9">
         <v>0</v>
       </c>
       <c r="S42" s="9">
+        <v>0</v>
+      </c>
+      <c r="T42" s="9">
         <v>1914</v>
       </c>
-      <c r="T42" s="10">
+      <c r="U42" s="10">
         <v>-0.15</v>
       </c>
-      <c r="U42" s="9">
+      <c r="V42" s="9">
         <v>70</v>
       </c>
-      <c r="V42" s="10">
+      <c r="W42" s="10">
         <v>-0.05</v>
       </c>
-      <c r="W42" s="9">
+      <c r="X42" s="9">
         <v>64</v>
       </c>
-      <c r="X42" s="9">
+      <c r="Y42" s="9">
         <v>108</v>
       </c>
-      <c r="Y42" s="9">
+      <c r="Z42" s="9">
         <v>106</v>
       </c>
-      <c r="Z42" s="9">
+      <c r="AA42" s="9">
         <v>108</v>
       </c>
-      <c r="AA42" s="9">
+      <c r="AB42" s="9">
         <v>307</v>
       </c>
-      <c r="AB42" s="9">
+      <c r="AC42" s="9">
         <v>108</v>
       </c>
-      <c r="AC42" s="9">
+      <c r="AD42" s="9">
         <v>96</v>
       </c>
-      <c r="AD42" s="9">
+      <c r="AE42" s="9">
         <v>102</v>
       </c>
-      <c r="AE42" s="9"/>
-      <c r="AF42" s="9">
+      <c r="AF42" s="9"/>
+      <c r="AG42" s="9">
         <v>12</v>
       </c>
-      <c r="AG42" s="9">
+      <c r="AH42" s="9">
         <v>485</v>
       </c>
-      <c r="AH42" s="9">
+      <c r="AI42" s="9">
         <v>650</v>
       </c>
-      <c r="AI42" s="9">
+      <c r="AJ42" s="9">
         <v>105</v>
       </c>
-      <c r="AJ42" s="9">
+      <c r="AK42" s="9">
         <v>6</v>
       </c>
-      <c r="AK42" s="9">
+      <c r="AL42" s="9">
         <v>107</v>
       </c>
-      <c r="AL42" s="9">
+      <c r="AM42" s="9">
         <v>111</v>
       </c>
-      <c r="AM42" s="9">
+      <c r="AN42" s="9">
         <v>103</v>
       </c>
-      <c r="AN42" s="9">
+      <c r="AO42" s="9">
         <v>99</v>
       </c>
-      <c r="AO42" s="9">
+      <c r="AP42" s="9">
         <v>100</v>
       </c>
-      <c r="AP42" s="9">
+      <c r="AQ42" s="9">
         <v>99</v>
       </c>
-      <c r="AQ42" s="9">
+      <c r="AR42" s="9">
         <v>101</v>
       </c>
     </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
         <v>312</v>
       </c>
@@ -7583,102 +7813,105 @@
       <c r="K43" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="L43" s="2">
+      <c r="L43" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="M43" s="2">
         <v>45164</v>
       </c>
-      <c r="M43" s="4" t="s">
+      <c r="N43" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N43" s="2" t="s">
+      <c r="O43" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O43" s="5" t="s">
+      <c r="P43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="P43" s="9">
+      <c r="Q43" s="9">
         <v>79</v>
-      </c>
-      <c r="Q43" s="9">
-        <v>0</v>
       </c>
       <c r="R43" s="9">
         <v>0</v>
       </c>
       <c r="S43" s="9">
+        <v>0</v>
+      </c>
+      <c r="T43" s="9">
         <v>1014</v>
       </c>
-      <c r="T43" s="10">
+      <c r="U43" s="10">
         <v>0.2</v>
       </c>
-      <c r="U43" s="9">
+      <c r="V43" s="9">
         <v>65</v>
       </c>
-      <c r="V43" s="10">
+      <c r="W43" s="10">
         <v>0.11</v>
       </c>
-      <c r="W43" s="9">
+      <c r="X43" s="9">
         <v>47</v>
       </c>
-      <c r="X43" s="9">
+      <c r="Y43" s="9">
         <v>109</v>
       </c>
-      <c r="Y43" s="9">
+      <c r="Z43" s="9">
         <v>104</v>
       </c>
-      <c r="Z43" s="9">
+      <c r="AA43" s="9">
         <v>109</v>
       </c>
-      <c r="AA43" s="9">
+      <c r="AB43" s="9">
         <v>234</v>
       </c>
-      <c r="AB43" s="9">
+      <c r="AC43" s="9">
         <v>103</v>
       </c>
-      <c r="AC43" s="9">
+      <c r="AD43" s="9">
         <v>97</v>
       </c>
-      <c r="AD43" s="9">
+      <c r="AE43" s="9">
         <v>100</v>
       </c>
-      <c r="AE43" s="9"/>
-      <c r="AF43" s="9">
+      <c r="AF43" s="9"/>
+      <c r="AG43" s="9">
         <v>9</v>
       </c>
-      <c r="AG43" s="9">
+      <c r="AH43" s="9">
         <v>397</v>
       </c>
-      <c r="AH43" s="9">
+      <c r="AI43" s="9">
         <v>205</v>
       </c>
-      <c r="AI43" s="9">
+      <c r="AJ43" s="9">
         <v>104</v>
       </c>
-      <c r="AJ43" s="9">
+      <c r="AK43" s="9">
         <v>5</v>
       </c>
-      <c r="AK43" s="9">
+      <c r="AL43" s="9">
         <v>102</v>
       </c>
-      <c r="AL43" s="9">
+      <c r="AM43" s="9">
         <v>105</v>
       </c>
-      <c r="AM43" s="9">
+      <c r="AN43" s="9">
         <v>103</v>
       </c>
-      <c r="AN43" s="9">
+      <c r="AO43" s="9">
         <v>104</v>
       </c>
-      <c r="AO43" s="9">
+      <c r="AP43" s="9">
         <v>105</v>
-      </c>
-      <c r="AP43" s="9">
-        <v>101</v>
       </c>
       <c r="AQ43" s="9">
         <v>101</v>
       </c>
+      <c r="AR43" s="9">
+        <v>101</v>
+      </c>
     </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
         <v>304</v>
       </c>
@@ -7712,102 +7945,105 @@
       <c r="K44" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="L44" s="2">
+      <c r="L44" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M44" s="2">
         <v>45360</v>
       </c>
-      <c r="M44" s="4" t="s">
+      <c r="N44" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N44" s="2" t="s">
+      <c r="O44" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O44" s="5" t="s">
+      <c r="P44" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="P44" s="9">
+      <c r="Q44" s="9">
         <v>76</v>
-      </c>
-      <c r="Q44" s="9">
-        <v>0</v>
       </c>
       <c r="R44" s="9">
         <v>0</v>
       </c>
       <c r="S44" s="9">
+        <v>0</v>
+      </c>
+      <c r="T44" s="9">
         <v>807</v>
       </c>
-      <c r="T44" s="10">
+      <c r="U44" s="10">
         <v>0.28999999999999998</v>
       </c>
-      <c r="U44" s="9">
+      <c r="V44" s="9">
         <v>64</v>
       </c>
-      <c r="V44" s="10">
+      <c r="W44" s="10">
         <v>0.09</v>
       </c>
-      <c r="W44" s="9">
+      <c r="X44" s="9">
         <v>38</v>
-      </c>
-      <c r="X44" s="9">
-        <v>109</v>
       </c>
       <c r="Y44" s="9">
         <v>109</v>
       </c>
       <c r="Z44" s="9">
+        <v>109</v>
+      </c>
+      <c r="AA44" s="9">
         <v>111</v>
       </c>
-      <c r="AA44" s="9">
+      <c r="AB44" s="9">
         <v>308</v>
       </c>
-      <c r="AB44" s="9">
+      <c r="AC44" s="9">
         <v>111</v>
       </c>
-      <c r="AC44" s="9">
+      <c r="AD44" s="9">
         <v>95</v>
       </c>
-      <c r="AD44" s="9">
+      <c r="AE44" s="9">
         <v>102</v>
       </c>
-      <c r="AE44" s="9"/>
-      <c r="AF44" s="9">
+      <c r="AF44" s="9"/>
+      <c r="AG44" s="9">
         <v>13</v>
       </c>
-      <c r="AG44" s="9">
+      <c r="AH44" s="9">
         <v>355</v>
       </c>
-      <c r="AH44" s="9">
+      <c r="AI44" s="9">
         <v>670</v>
       </c>
-      <c r="AI44" s="9">
+      <c r="AJ44" s="9">
         <v>106</v>
       </c>
-      <c r="AJ44" s="9">
+      <c r="AK44" s="9">
         <v>8</v>
       </c>
-      <c r="AK44" s="9">
+      <c r="AL44" s="9">
         <v>110</v>
       </c>
-      <c r="AL44" s="9">
+      <c r="AM44" s="9">
         <v>109</v>
       </c>
-      <c r="AM44" s="9">
+      <c r="AN44" s="9">
         <v>107</v>
       </c>
-      <c r="AN44" s="9">
+      <c r="AO44" s="9">
         <v>106</v>
       </c>
-      <c r="AO44" s="9">
+      <c r="AP44" s="9">
         <v>100</v>
       </c>
-      <c r="AP44" s="9">
+      <c r="AQ44" s="9">
         <v>103</v>
       </c>
-      <c r="AQ44" s="9">
+      <c r="AR44" s="9">
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>293</v>
       </c>
@@ -7841,102 +8077,105 @@
       <c r="K45" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="L45" s="2">
+      <c r="L45" s="16" t="s">
+        <v>540</v>
+      </c>
+      <c r="M45" s="2">
         <v>44486</v>
       </c>
-      <c r="M45" s="4" t="s">
+      <c r="N45" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N45" s="3" t="s">
+      <c r="O45" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="O45" s="3" t="s">
+      <c r="P45" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="P45" s="9">
+      <c r="Q45" s="9">
         <v>80</v>
-      </c>
-      <c r="Q45" s="9">
-        <v>0</v>
       </c>
       <c r="R45" s="9">
         <v>0</v>
       </c>
       <c r="S45" s="9">
+        <v>0</v>
+      </c>
+      <c r="T45" s="9">
         <v>641</v>
       </c>
-      <c r="T45" s="10">
+      <c r="U45" s="10">
         <v>0.06</v>
       </c>
-      <c r="U45" s="9">
+      <c r="V45" s="9">
         <v>34</v>
       </c>
-      <c r="V45" s="10">
+      <c r="W45" s="10">
         <v>0.06</v>
       </c>
-      <c r="W45" s="9">
+      <c r="X45" s="9">
         <v>29</v>
       </c>
-      <c r="X45" s="9">
+      <c r="Y45" s="9">
         <v>107</v>
       </c>
-      <c r="Y45" s="9">
+      <c r="Z45" s="9">
         <v>106</v>
       </c>
-      <c r="Z45" s="9">
+      <c r="AA45" s="9">
         <v>109</v>
       </c>
-      <c r="AA45" s="9">
+      <c r="AB45" s="9">
         <v>263</v>
       </c>
-      <c r="AB45" s="9">
+      <c r="AC45" s="9">
         <v>101</v>
       </c>
-      <c r="AC45" s="9">
+      <c r="AD45" s="9">
         <v>97</v>
       </c>
-      <c r="AD45" s="9">
+      <c r="AE45" s="9">
         <v>107</v>
       </c>
-      <c r="AE45" s="9"/>
-      <c r="AF45" s="9">
+      <c r="AF45" s="9"/>
+      <c r="AG45" s="9">
         <v>11</v>
       </c>
-      <c r="AG45" s="9">
+      <c r="AH45" s="9">
         <v>227</v>
       </c>
-      <c r="AH45" s="9">
+      <c r="AI45" s="9">
         <v>991</v>
       </c>
-      <c r="AI45" s="9">
+      <c r="AJ45" s="9">
         <v>104</v>
       </c>
-      <c r="AJ45" s="9">
+      <c r="AK45" s="9">
         <v>7</v>
       </c>
-      <c r="AK45" s="9">
+      <c r="AL45" s="9">
         <v>104</v>
       </c>
-      <c r="AL45" s="9">
+      <c r="AM45" s="9">
         <v>112</v>
       </c>
-      <c r="AM45" s="9">
+      <c r="AN45" s="9">
         <v>105</v>
       </c>
-      <c r="AN45" s="9">
+      <c r="AO45" s="9">
         <v>101</v>
       </c>
-      <c r="AO45" s="9">
+      <c r="AP45" s="9">
         <v>103</v>
-      </c>
-      <c r="AP45" s="9">
-        <v>100</v>
       </c>
       <c r="AQ45" s="9">
         <v>100</v>
       </c>
+      <c r="AR45" s="9">
+        <v>100</v>
+      </c>
     </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>282</v>
       </c>
@@ -7970,102 +8209,105 @@
       <c r="K46" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="L46" s="2">
+      <c r="L46" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="M46" s="2">
         <v>43808</v>
       </c>
-      <c r="M46" s="4" t="s">
+      <c r="N46" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N46" s="3" t="s">
+      <c r="O46" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="O46" s="3" t="s">
+      <c r="P46" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="P46" s="9">
+      <c r="Q46" s="9">
         <v>95</v>
       </c>
-      <c r="Q46" s="9">
+      <c r="R46" s="9">
         <v>822</v>
       </c>
-      <c r="R46" s="9">
+      <c r="S46" s="9">
         <v>347</v>
       </c>
-      <c r="S46" s="9">
+      <c r="T46" s="9">
         <v>774</v>
       </c>
-      <c r="T46" s="10">
+      <c r="U46" s="10">
         <v>-0.18</v>
       </c>
-      <c r="U46" s="9">
+      <c r="V46" s="9">
         <v>17</v>
       </c>
-      <c r="V46" s="10">
+      <c r="W46" s="10">
         <v>-0.01</v>
       </c>
-      <c r="W46" s="9">
+      <c r="X46" s="9">
         <v>27</v>
       </c>
-      <c r="X46" s="9">
+      <c r="Y46" s="9">
         <v>111</v>
       </c>
-      <c r="Y46" s="9">
+      <c r="Z46" s="9">
         <v>106</v>
       </c>
-      <c r="Z46" s="9">
+      <c r="AA46" s="9">
         <v>110</v>
       </c>
-      <c r="AA46" s="9">
+      <c r="AB46" s="9">
         <v>186</v>
       </c>
-      <c r="AB46" s="9">
+      <c r="AC46" s="9">
         <v>108</v>
       </c>
-      <c r="AC46" s="9">
+      <c r="AD46" s="9">
         <v>93</v>
       </c>
-      <c r="AD46" s="9">
+      <c r="AE46" s="9">
         <v>99</v>
       </c>
-      <c r="AE46" s="9"/>
-      <c r="AF46" s="9">
+      <c r="AF46" s="9"/>
+      <c r="AG46" s="9">
         <v>9</v>
       </c>
-      <c r="AG46" s="9">
+      <c r="AH46" s="9">
         <v>167</v>
       </c>
-      <c r="AH46" s="9">
+      <c r="AI46" s="9">
         <v>419</v>
       </c>
-      <c r="AI46" s="9">
+      <c r="AJ46" s="9">
         <v>103</v>
       </c>
-      <c r="AJ46" s="9">
+      <c r="AK46" s="9">
         <v>6</v>
       </c>
-      <c r="AK46" s="9">
+      <c r="AL46" s="9">
         <v>106</v>
       </c>
-      <c r="AL46" s="9">
+      <c r="AM46" s="9">
         <v>105</v>
       </c>
-      <c r="AM46" s="9">
+      <c r="AN46" s="9">
         <v>109</v>
       </c>
-      <c r="AN46" s="9">
+      <c r="AO46" s="9">
         <v>106</v>
       </c>
-      <c r="AO46" s="9">
+      <c r="AP46" s="9">
         <v>100</v>
       </c>
-      <c r="AP46" s="9">
+      <c r="AQ46" s="9">
         <v>95</v>
       </c>
-      <c r="AQ46" s="9">
+      <c r="AR46" s="9">
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>274</v>
       </c>
@@ -8099,102 +8341,105 @@
       <c r="K47" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="L47" s="2">
+      <c r="L47" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="M47" s="2">
         <v>44108</v>
       </c>
-      <c r="M47" s="4" t="s">
+      <c r="N47" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N47" s="3" t="s">
+      <c r="O47" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="O47" s="3" t="s">
+      <c r="P47" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="P47" s="9">
+      <c r="Q47" s="9">
         <v>90</v>
       </c>
-      <c r="Q47" s="9">
+      <c r="R47" s="9">
         <v>1412</v>
       </c>
-      <c r="R47" s="9">
+      <c r="S47" s="9">
         <v>593</v>
       </c>
-      <c r="S47" s="9">
+      <c r="T47" s="9">
         <v>294</v>
       </c>
-      <c r="T47" s="10">
+      <c r="U47" s="10">
         <v>0.36</v>
       </c>
-      <c r="U47" s="9">
+      <c r="V47" s="9">
         <v>46</v>
       </c>
-      <c r="V47" s="10">
+      <c r="W47" s="10">
         <v>0.15</v>
       </c>
-      <c r="W47" s="9">
+      <c r="X47" s="9">
         <v>24</v>
       </c>
-      <c r="X47" s="9">
+      <c r="Y47" s="9">
         <v>108</v>
       </c>
-      <c r="Y47" s="9">
+      <c r="Z47" s="9">
         <v>106</v>
       </c>
-      <c r="Z47" s="9">
+      <c r="AA47" s="9">
         <v>110</v>
       </c>
-      <c r="AA47" s="9">
+      <c r="AB47" s="9">
         <v>121</v>
       </c>
-      <c r="AB47" s="9">
+      <c r="AC47" s="9">
         <v>99</v>
       </c>
-      <c r="AC47" s="9">
+      <c r="AD47" s="9">
         <v>105</v>
       </c>
-      <c r="AD47" s="9">
+      <c r="AE47" s="9">
         <v>113</v>
       </c>
-      <c r="AE47" s="9"/>
-      <c r="AF47" s="9">
+      <c r="AF47" s="9"/>
+      <c r="AG47" s="9">
         <v>4</v>
       </c>
-      <c r="AG47" s="9">
+      <c r="AH47" s="9">
         <v>241</v>
       </c>
-      <c r="AH47" s="9">
+      <c r="AI47" s="9">
         <v>276</v>
       </c>
-      <c r="AI47" s="9">
+      <c r="AJ47" s="9">
         <v>100</v>
       </c>
-      <c r="AJ47" s="9">
+      <c r="AK47" s="9">
         <v>2</v>
       </c>
-      <c r="AK47" s="9">
+      <c r="AL47" s="9">
         <v>100</v>
       </c>
-      <c r="AL47" s="9">
+      <c r="AM47" s="9">
         <v>104</v>
       </c>
-      <c r="AM47" s="9">
+      <c r="AN47" s="9">
         <v>105</v>
       </c>
-      <c r="AN47" s="9">
+      <c r="AO47" s="9">
         <v>97</v>
       </c>
-      <c r="AO47" s="9">
+      <c r="AP47" s="9">
         <v>98</v>
       </c>
-      <c r="AP47" s="9">
+      <c r="AQ47" s="9">
         <v>101</v>
       </c>
-      <c r="AQ47" s="9">
+      <c r="AR47" s="9">
         <v>102</v>
       </c>
     </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>263</v>
       </c>
@@ -8228,102 +8473,105 @@
       <c r="K48" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="L48" s="2">
+      <c r="L48" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="M48" s="2">
         <v>44476</v>
       </c>
-      <c r="M48" s="4" t="s">
+      <c r="N48" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N48" s="3" t="s">
+      <c r="O48" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O48" s="3" t="s">
+      <c r="P48" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="P48" s="9">
+      <c r="Q48" s="9">
         <v>82</v>
-      </c>
-      <c r="Q48" s="9">
-        <v>0</v>
       </c>
       <c r="R48" s="9">
         <v>0</v>
       </c>
       <c r="S48" s="9">
+        <v>0</v>
+      </c>
+      <c r="T48" s="9">
         <v>200</v>
       </c>
-      <c r="T48" s="10">
+      <c r="U48" s="10">
         <v>0.92</v>
       </c>
-      <c r="U48" s="9">
+      <c r="V48" s="9">
         <v>92</v>
       </c>
-      <c r="V48" s="10">
+      <c r="W48" s="10">
         <v>0.28999999999999998</v>
       </c>
-      <c r="W48" s="9">
+      <c r="X48" s="9">
         <v>33</v>
       </c>
-      <c r="X48" s="9">
+      <c r="Y48" s="9">
         <v>112</v>
       </c>
-      <c r="Y48" s="9">
+      <c r="Z48" s="9">
         <v>104</v>
       </c>
-      <c r="Z48" s="9">
+      <c r="AA48" s="9">
         <v>110</v>
       </c>
-      <c r="AA48" s="9">
+      <c r="AB48" s="9">
         <v>185</v>
       </c>
-      <c r="AB48" s="9">
+      <c r="AC48" s="9">
         <v>103</v>
       </c>
-      <c r="AC48" s="9">
+      <c r="AD48" s="9">
         <v>99</v>
       </c>
-      <c r="AD48" s="9">
+      <c r="AE48" s="9">
         <v>115</v>
       </c>
-      <c r="AE48" s="9"/>
-      <c r="AF48" s="9">
+      <c r="AF48" s="9"/>
+      <c r="AG48" s="9">
         <v>3</v>
       </c>
-      <c r="AG48" s="9">
+      <c r="AH48" s="9">
         <v>418</v>
       </c>
-      <c r="AH48" s="9">
+      <c r="AI48" s="9">
         <v>113</v>
       </c>
-      <c r="AI48" s="9">
+      <c r="AJ48" s="9">
         <v>99</v>
       </c>
-      <c r="AJ48" s="9">
+      <c r="AK48" s="9">
         <v>3</v>
       </c>
-      <c r="AK48" s="9">
+      <c r="AL48" s="9">
         <v>104</v>
       </c>
-      <c r="AL48" s="9">
+      <c r="AM48" s="9">
         <v>105</v>
       </c>
-      <c r="AM48" s="9">
+      <c r="AN48" s="9">
         <v>106</v>
       </c>
-      <c r="AN48" s="9">
+      <c r="AO48" s="9">
         <v>101</v>
       </c>
-      <c r="AO48" s="9">
+      <c r="AP48" s="9">
         <v>97</v>
       </c>
-      <c r="AP48" s="9">
+      <c r="AQ48" s="9">
         <v>98</v>
       </c>
-      <c r="AQ48" s="9">
+      <c r="AR48" s="9">
         <v>105</v>
       </c>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>219</v>
       </c>
@@ -8357,104 +8605,107 @@
       <c r="K49" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="L49" s="2">
+      <c r="L49" s="16" t="s">
+        <v>560</v>
+      </c>
+      <c r="M49" s="2">
         <v>44164</v>
       </c>
-      <c r="M49" s="4" t="s">
+      <c r="N49" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N49" s="5" t="s">
+      <c r="O49" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="O49" s="5" t="s">
+      <c r="P49" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="P49" s="9">
+      <c r="Q49" s="9">
         <v>98</v>
       </c>
-      <c r="Q49" s="9">
+      <c r="R49" s="9">
         <v>902</v>
       </c>
-      <c r="R49" s="9">
+      <c r="S49" s="9">
         <v>132</v>
       </c>
-      <c r="S49" s="9">
+      <c r="T49" s="9">
         <v>353</v>
       </c>
-      <c r="T49" s="10">
+      <c r="U49" s="10">
         <v>0.09</v>
       </c>
-      <c r="U49" s="9">
+      <c r="V49" s="9">
         <v>38</v>
       </c>
-      <c r="V49" s="10">
+      <c r="W49" s="10">
         <v>0.04</v>
       </c>
-      <c r="W49" s="9">
+      <c r="X49" s="9">
         <v>22</v>
       </c>
-      <c r="X49" s="9">
+      <c r="Y49" s="9">
         <v>1.51</v>
       </c>
-      <c r="Y49" s="9">
+      <c r="Z49" s="9">
         <v>1.18</v>
       </c>
-      <c r="Z49" s="9">
+      <c r="AA49" s="9">
         <v>1.75</v>
       </c>
-      <c r="AA49" s="9">
+      <c r="AB49" s="9">
         <v>2920</v>
       </c>
-      <c r="AB49" s="9">
+      <c r="AC49" s="9">
         <v>344</v>
       </c>
-      <c r="AC49" s="9">
+      <c r="AD49" s="9">
         <v>3.05</v>
       </c>
-      <c r="AD49" s="9">
+      <c r="AE49" s="9">
         <v>1.3</v>
       </c>
-      <c r="AE49" s="9">
+      <c r="AF49" s="9">
         <v>96</v>
       </c>
-      <c r="AF49" s="9">
+      <c r="AG49" s="9">
         <v>100</v>
       </c>
-      <c r="AG49" s="9">
+      <c r="AH49" s="9">
         <v>9</v>
       </c>
-      <c r="AH49" s="9">
+      <c r="AI49" s="9">
         <v>329</v>
       </c>
-      <c r="AI49" s="9">
+      <c r="AJ49" s="9">
         <v>105</v>
       </c>
-      <c r="AJ49" s="9">
+      <c r="AK49" s="9">
         <v>2</v>
       </c>
-      <c r="AK49" s="9">
+      <c r="AL49" s="9">
         <v>94</v>
       </c>
-      <c r="AL49" s="9">
+      <c r="AM49" s="9">
         <v>104</v>
       </c>
-      <c r="AM49" s="9">
+      <c r="AN49" s="9">
         <v>102</v>
       </c>
-      <c r="AN49" s="9">
+      <c r="AO49" s="9">
         <v>1.9</v>
       </c>
-      <c r="AO49" s="9">
+      <c r="AP49" s="9">
         <v>-1</v>
       </c>
-      <c r="AP49" s="9">
+      <c r="AQ49" s="9">
         <v>0.39</v>
       </c>
-      <c r="AQ49" s="9">
+      <c r="AR49" s="9">
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>230</v>
       </c>
@@ -8488,104 +8739,107 @@
       <c r="K50" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="L50" s="2">
+      <c r="L50" s="16" t="s">
+        <v>561</v>
+      </c>
+      <c r="M50" s="2">
         <v>43891</v>
       </c>
-      <c r="M50" s="4" t="s">
+      <c r="N50" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N50" s="5" t="s">
+      <c r="O50" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="O50" s="5" t="s">
+      <c r="P50" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="P50" s="9">
+      <c r="Q50" s="9">
         <v>97</v>
       </c>
-      <c r="Q50" s="9">
+      <c r="R50" s="9">
         <v>1059</v>
       </c>
-      <c r="R50" s="9">
+      <c r="S50" s="9">
         <v>169</v>
       </c>
-      <c r="S50" s="9">
+      <c r="T50" s="9">
         <v>2050</v>
       </c>
-      <c r="T50" s="10">
+      <c r="U50" s="10">
         <v>-0.08</v>
       </c>
-      <c r="U50" s="9">
+      <c r="V50" s="9">
         <v>61</v>
       </c>
-      <c r="V50" s="10">
+      <c r="W50" s="10">
         <v>-0.04</v>
       </c>
-      <c r="W50" s="9">
+      <c r="X50" s="9">
         <v>55</v>
       </c>
-      <c r="X50" s="9">
+      <c r="Y50" s="9">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Y50" s="9">
+      <c r="Z50" s="9">
         <v>-0.48</v>
       </c>
-      <c r="Z50" s="9">
+      <c r="AA50" s="9">
         <v>0.31</v>
       </c>
-      <c r="AA50" s="9">
+      <c r="AB50" s="9">
         <v>2937</v>
       </c>
-      <c r="AB50" s="9">
+      <c r="AC50" s="9">
         <v>508</v>
       </c>
-      <c r="AC50" s="9">
+      <c r="AD50" s="9">
         <v>3.37</v>
       </c>
-      <c r="AD50" s="9">
+      <c r="AE50" s="9">
         <v>0.4</v>
       </c>
-      <c r="AE50" s="9">
+      <c r="AF50" s="9">
         <v>98</v>
       </c>
-      <c r="AF50" s="9">
+      <c r="AG50" s="9">
         <v>104</v>
       </c>
-      <c r="AG50" s="9">
+      <c r="AH50" s="9">
         <v>14</v>
       </c>
-      <c r="AH50" s="9">
+      <c r="AI50" s="9">
         <v>525</v>
       </c>
-      <c r="AI50" s="9">
+      <c r="AJ50" s="9">
         <v>112</v>
       </c>
-      <c r="AJ50" s="9">
+      <c r="AK50" s="9">
         <v>-1</v>
-      </c>
-      <c r="AK50" s="9">
-        <v>96</v>
       </c>
       <c r="AL50" s="9">
         <v>96</v>
       </c>
       <c r="AM50" s="9">
+        <v>96</v>
+      </c>
+      <c r="AN50" s="9">
         <v>100</v>
       </c>
-      <c r="AN50" s="9">
+      <c r="AO50" s="9">
         <v>1.3</v>
       </c>
-      <c r="AO50" s="9">
+      <c r="AP50" s="9">
         <v>-2</v>
       </c>
-      <c r="AP50" s="9">
+      <c r="AQ50" s="9">
         <v>0.08</v>
       </c>
-      <c r="AQ50" s="9">
+      <c r="AR50" s="9">
         <v>0.16</v>
       </c>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>252</v>
       </c>
@@ -8619,102 +8873,105 @@
       <c r="K51" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="L51" s="2">
+      <c r="L51" s="16" t="s">
+        <v>561</v>
+      </c>
+      <c r="M51" s="2">
         <v>44545</v>
       </c>
-      <c r="M51" s="4" t="s">
+      <c r="N51" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N51" s="5" t="s">
+      <c r="O51" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="O51" s="5" t="s">
+      <c r="P51" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="P51" s="9">
+      <c r="Q51" s="9">
         <v>82</v>
-      </c>
-      <c r="Q51" s="9">
-        <v>0</v>
       </c>
       <c r="R51" s="9">
         <v>0</v>
       </c>
       <c r="S51" s="9">
+        <v>0</v>
+      </c>
+      <c r="T51" s="9">
         <v>731</v>
       </c>
-      <c r="T51" s="10">
+      <c r="U51" s="10">
         <v>0.12</v>
       </c>
-      <c r="U51" s="9">
+      <c r="V51" s="9">
         <v>64</v>
       </c>
-      <c r="V51" s="10">
+      <c r="W51" s="10">
         <v>0.06</v>
       </c>
-      <c r="W51" s="9">
+      <c r="X51" s="9">
         <v>40</v>
       </c>
-      <c r="X51" s="9">
+      <c r="Y51" s="9">
         <v>-0.22</v>
       </c>
-      <c r="Y51" s="9">
+      <c r="Z51" s="9">
         <v>0.85</v>
       </c>
-      <c r="Z51" s="9">
+      <c r="AA51" s="9">
         <v>0.95</v>
       </c>
-      <c r="AA51" s="9">
+      <c r="AB51" s="9">
         <v>3146</v>
       </c>
-      <c r="AB51" s="9">
+      <c r="AC51" s="9">
         <v>680</v>
       </c>
-      <c r="AC51" s="9">
+      <c r="AD51" s="9">
         <v>2.89</v>
       </c>
-      <c r="AD51" s="9">
+      <c r="AE51" s="9">
         <v>3.4</v>
       </c>
-      <c r="AE51" s="9">
+      <c r="AF51" s="9">
         <v>101</v>
       </c>
-      <c r="AF51" s="9"/>
-      <c r="AG51" s="9">
+      <c r="AG51" s="9"/>
+      <c r="AH51" s="9">
         <v>12</v>
       </c>
-      <c r="AH51" s="9">
+      <c r="AI51" s="9">
         <v>652</v>
       </c>
-      <c r="AI51" s="9">
+      <c r="AJ51" s="9">
         <v>107</v>
       </c>
-      <c r="AJ51" s="9">
+      <c r="AK51" s="9">
         <v>3</v>
       </c>
-      <c r="AK51" s="9">
+      <c r="AL51" s="9">
         <v>103</v>
       </c>
-      <c r="AL51" s="9">
+      <c r="AM51" s="9">
         <v>100</v>
       </c>
-      <c r="AM51" s="9">
+      <c r="AN51" s="9">
         <v>99</v>
       </c>
-      <c r="AN51" s="9">
+      <c r="AO51" s="9">
         <v>1.2</v>
       </c>
-      <c r="AO51" s="9">
+      <c r="AP51" s="9">
         <v>-0.1</v>
       </c>
-      <c r="AP51" s="9">
+      <c r="AQ51" s="9">
         <v>0.86</v>
       </c>
-      <c r="AQ51" s="9">
+      <c r="AR51" s="9">
         <v>-0.11</v>
       </c>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>241</v>
       </c>
@@ -8748,100 +9005,103 @@
       <c r="K52" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="L52" s="2">
+      <c r="L52" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="M52" s="2">
         <v>44493</v>
       </c>
-      <c r="M52" s="4" t="s">
+      <c r="N52" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N52" s="5" t="s">
+      <c r="O52" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="O52" s="5" t="s">
+      <c r="P52" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="P52" s="9">
+      <c r="Q52" s="9">
         <v>85</v>
-      </c>
-      <c r="Q52" s="9">
-        <v>0</v>
       </c>
       <c r="R52" s="9">
         <v>0</v>
       </c>
       <c r="S52" s="9">
+        <v>0</v>
+      </c>
+      <c r="T52" s="9">
         <v>1436</v>
       </c>
-      <c r="T52" s="10">
+      <c r="U52" s="10">
         <v>0.11</v>
       </c>
-      <c r="U52" s="9">
+      <c r="V52" s="9">
         <v>91</v>
       </c>
-      <c r="V52" s="10">
+      <c r="W52" s="10">
         <v>0.06</v>
       </c>
-      <c r="W52" s="9">
+      <c r="X52" s="9">
         <v>65</v>
       </c>
-      <c r="X52" s="9">
+      <c r="Y52" s="9">
         <v>-0.48</v>
       </c>
-      <c r="Y52" s="9">
+      <c r="Z52" s="9">
         <v>1.1299999999999999</v>
       </c>
-      <c r="Z52" s="9">
+      <c r="AA52" s="9">
         <v>0.61</v>
       </c>
-      <c r="AA52" s="9">
+      <c r="AB52" s="9">
         <v>3151</v>
       </c>
-      <c r="AB52" s="9">
+      <c r="AC52" s="9">
         <v>663</v>
       </c>
-      <c r="AC52" s="9">
+      <c r="AD52" s="9">
         <v>3.06</v>
       </c>
-      <c r="AD52" s="9">
+      <c r="AE52" s="9">
         <v>-0.5</v>
       </c>
-      <c r="AE52" s="9">
+      <c r="AF52" s="9">
         <v>108</v>
       </c>
-      <c r="AF52" s="9">
+      <c r="AG52" s="9">
         <v>89</v>
       </c>
-      <c r="AG52" s="9">
+      <c r="AH52" s="9">
         <v>11</v>
       </c>
-      <c r="AH52" s="9">
+      <c r="AI52" s="9">
         <v>634</v>
       </c>
-      <c r="AI52" s="9">
+      <c r="AJ52" s="9">
         <v>106</v>
       </c>
-      <c r="AJ52" s="9">
+      <c r="AK52" s="9">
         <v>1</v>
-      </c>
-      <c r="AK52" s="9">
-        <v>99</v>
       </c>
       <c r="AL52" s="9">
         <v>99</v>
       </c>
       <c r="AM52" s="9">
+        <v>99</v>
+      </c>
+      <c r="AN52" s="9">
         <v>98</v>
       </c>
-      <c r="AN52" s="9">
+      <c r="AO52" s="9">
         <v>1.2</v>
       </c>
-      <c r="AO52" s="9">
+      <c r="AP52" s="9">
         <v>-3.6</v>
       </c>
-      <c r="AP52" s="9">
+      <c r="AQ52" s="9">
         <v>0.34</v>
       </c>
-      <c r="AQ52" s="9">
+      <c r="AR52" s="9">
         <v>0.3</v>
       </c>
     </row>
@@ -8850,7 +9110,7 @@
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="P2:AQ22 R1 X1 AA1:AB1 AF1:AG1 AJ1 AM1 L2:L22 P24:AQ28 V23:AQ23 L24:L28" numberStoredAsText="1"/>
+    <ignoredError sqref="Q2:AR22 S1 Y1 AB1:AC1 AG1:AH1 AK1 AN1 M2:M22 Q24:AR28 W23:AR23 M24:M28" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>